--- a/public/templates/TFPL_schedule_template.xlsx
+++ b/public/templates/TFPL_schedule_template.xlsx
@@ -335,217 +335,219 @@
     <t>N세트 종류</t>
   </si>
   <si>
+    <t>N세트 맵</t>
+  </si>
+  <si>
+    <t>에결 맵</t>
+  </si>
+  <si>
+    <t>7세트(플레이오프는 9세트) ACE 결정전 맵. 3:3(플레이오프 4:4)일 때만 해요.</t>
+  </si>
+  <si>
+    <t>시간 (선택)</t>
+  </si>
+  <si>
+    <t>비우면 21:00</t>
+  </si>
+  <si>
+    <t>엔트리 공개 (선택)</t>
+  </si>
+  <si>
+    <t>비우면 경기 당일 19:00. 엔트리 마감은 공개 2시간 전(17:00)이에요.</t>
+  </si>
+  <si>
+    <t>메모 (선택)</t>
+  </si>
+  <si>
+    <t>자유롭게 (예: 중계 BJ, 연기 사유)</t>
+  </si>
+  <si>
+    <t>경기코드 · 요일 · 확인</t>
+  </si>
+  <si>
+    <t>자동으로 채워지는 칸이라 손대지 마세요.</t>
+  </si>
+  <si>
+    <t>예시 (정규라운드 시트에 이렇게 들어가요 — 지난 시즌 1R-M1 기준)</t>
+  </si>
+  <si>
+    <t>홈팀</t>
+  </si>
+  <si>
+    <t>원정팀</t>
+  </si>
+  <si>
+    <t>1세트 종류</t>
+  </si>
+  <si>
+    <t>1세트 맵</t>
+  </si>
+  <si>
+    <t>2세트 종류</t>
+  </si>
+  <si>
+    <t>2세트 맵</t>
+  </si>
+  <si>
+    <t>3세트 종류</t>
+  </si>
+  <si>
+    <t>3세트 맵</t>
+  </si>
+  <si>
+    <t>4세트 종류</t>
+  </si>
+  <si>
+    <t>4세트 맵</t>
+  </si>
+  <si>
+    <t>5세트 종류</t>
+  </si>
+  <si>
+    <t>5세트 맵</t>
+  </si>
+  <si>
+    <t>6세트 종류</t>
+  </si>
+  <si>
+    <t>6세트 맵</t>
+  </si>
+  <si>
+    <t>1R</t>
+  </si>
+  <si>
+    <t>5월 5일</t>
+  </si>
+  <si>
+    <t>만능브라더스</t>
+  </si>
+  <si>
+    <t>언더독 S5</t>
+  </si>
+  <si>
+    <t>1티어</t>
+  </si>
+  <si>
+    <t>제인도</t>
+  </si>
+  <si>
+    <t>2티어</t>
+  </si>
+  <si>
+    <t>매치포인트</t>
+  </si>
+  <si>
+    <t>3티어</t>
+  </si>
+  <si>
+    <t>실피드</t>
+  </si>
+  <si>
+    <t>팀플2</t>
+  </si>
+  <si>
+    <t>빅헌터</t>
+  </si>
+  <si>
+    <t>4티어</t>
+  </si>
+  <si>
+    <t>폴리포이드</t>
+  </si>
+  <si>
+    <t>홈지정</t>
+  </si>
+  <si>
+    <t>녹아웃</t>
+  </si>
+  <si>
+    <t>애티튜드</t>
+  </si>
+  <si>
+    <t>※ 예시 줄은 이 안내 시트에만 있어요. 입력 시트는 빈 상태에서 시작해요.</t>
+  </si>
+  <si>
+    <t>경기코드 (자동)</t>
+  </si>
+  <si>
+    <t>요일 (자동)</t>
+  </si>
+  <si>
+    <t>확인 (자동)</t>
+  </si>
+  <si>
+    <t>7세트 종류</t>
+  </si>
+  <si>
+    <t>7세트 맵</t>
+  </si>
+  <si>
+    <t>8세트 종류</t>
+  </si>
+  <si>
+    <t>8세트 맵</t>
+  </si>
+  <si>
+    <t>팀 이름</t>
+  </si>
+  <si>
+    <t>맵</t>
+  </si>
+  <si>
+    <t>세트 종류 (정규)</t>
+  </si>
+  <si>
+    <t>세트 종류 (플레이오프)</t>
+  </si>
+  <si>
+    <t>이 시트 쓰는 법</t>
+  </si>
+  <si>
+    <t>• A열 팀 이름: 이번 시즌 팀 이름을 먼저 적어 주세요. 사이트 'PL 관리 › 팀 · 선수단'에 등록한 이름과 글자 하나까지 똑같아야 해요.</t>
+  </si>
+  <si>
+    <t>• B열 맵: 지금은 지난 시즌 맵이 예시로 들어 있어요. 이번 시즌 맵풀로 바꿔 주세요 (사이트 '맵풀'과 같은 이름).</t>
+  </si>
+  <si>
+    <t>• C · D열 세트 종류는 고정 값이라 고치지 마세요.</t>
+  </si>
+  <si>
+    <t>• 여기 적은 팀 · 맵이 '정규라운드' · '플레이오프' 시트의 드롭다운 목록이 돼요.</t>
+  </si>
+  <si>
+    <t>팀플3</t>
+  </si>
+  <si>
+    <t>옥타곤</t>
+  </si>
+  <si>
+    <t>팀플4</t>
+  </si>
+  <si>
+    <t>폴스타</t>
+  </si>
+  <si>
+    <t>루나</t>
+  </si>
+  <si>
+    <t>어웨이지정</t>
+  </si>
+  <si>
+    <t>헌터리스</t>
+  </si>
+  <si>
+    <t>레퀴엠</t>
+  </si>
+  <si>
     <t>1티어 · 2티어 · 3티어 · 4티어 = 그 티어 선수만 나가는 개인전
 팀플2 · 팀플3 · 팀플4 = 2:2 · 3:3 · 4:4 (팀플은 인원까지 꼭 구분)
-홈지정 = 홈팀이 개인전/팀플 중에서 고르는 세트
+홈지정 = 홈팀이 지정 티어 개인전(1~4티어 중 선택) 또는 생컨(2:2 · 폴리포이드 · 티어합 지정) 중에서 고르는 세트
 어웨이지정 = 원정팀이 고르는 세트 (플레이오프만)</t>
-  </si>
-  <si>
-    <t>N세트 맵</t>
-  </si>
-  <si>
-    <t>그 세트 맵. 홈지정 · 어웨이지정 세트는 '개인전을 고르면 쓰는 맵'을 적어요 (팀플을 고르면 그 팀이 맵풀에서 맵을 골라요).</t>
-  </si>
-  <si>
-    <t>에결 맵</t>
-  </si>
-  <si>
-    <t>7세트(플레이오프는 9세트) ACE 결정전 맵. 3:3(플레이오프 4:4)일 때만 해요.</t>
-  </si>
-  <si>
-    <t>시간 (선택)</t>
-  </si>
-  <si>
-    <t>비우면 21:00</t>
-  </si>
-  <si>
-    <t>엔트리 공개 (선택)</t>
-  </si>
-  <si>
-    <t>비우면 경기 당일 19:00. 엔트리 마감은 공개 2시간 전(17:00)이에요.</t>
-  </si>
-  <si>
-    <t>메모 (선택)</t>
-  </si>
-  <si>
-    <t>자유롭게 (예: 중계 BJ, 연기 사유)</t>
-  </si>
-  <si>
-    <t>경기코드 · 요일 · 확인</t>
-  </si>
-  <si>
-    <t>자동으로 채워지는 칸이라 손대지 마세요.</t>
-  </si>
-  <si>
-    <t>예시 (정규라운드 시트에 이렇게 들어가요 — 지난 시즌 1R-M1 기준)</t>
-  </si>
-  <si>
-    <t>홈팀</t>
-  </si>
-  <si>
-    <t>원정팀</t>
-  </si>
-  <si>
-    <t>1세트 종류</t>
-  </si>
-  <si>
-    <t>1세트 맵</t>
-  </si>
-  <si>
-    <t>2세트 종류</t>
-  </si>
-  <si>
-    <t>2세트 맵</t>
-  </si>
-  <si>
-    <t>3세트 종류</t>
-  </si>
-  <si>
-    <t>3세트 맵</t>
-  </si>
-  <si>
-    <t>4세트 종류</t>
-  </si>
-  <si>
-    <t>4세트 맵</t>
-  </si>
-  <si>
-    <t>5세트 종류</t>
-  </si>
-  <si>
-    <t>5세트 맵</t>
-  </si>
-  <si>
-    <t>6세트 종류</t>
-  </si>
-  <si>
-    <t>6세트 맵</t>
-  </si>
-  <si>
-    <t>1R</t>
-  </si>
-  <si>
-    <t>5월 5일</t>
-  </si>
-  <si>
-    <t>만능브라더스</t>
-  </si>
-  <si>
-    <t>언더독 S5</t>
-  </si>
-  <si>
-    <t>1티어</t>
-  </si>
-  <si>
-    <t>제인도</t>
-  </si>
-  <si>
-    <t>2티어</t>
-  </si>
-  <si>
-    <t>매치포인트</t>
-  </si>
-  <si>
-    <t>3티어</t>
-  </si>
-  <si>
-    <t>실피드</t>
-  </si>
-  <si>
-    <t>팀플2</t>
-  </si>
-  <si>
-    <t>빅헌터</t>
-  </si>
-  <si>
-    <t>4티어</t>
-  </si>
-  <si>
-    <t>폴리포이드</t>
-  </si>
-  <si>
-    <t>홈지정</t>
-  </si>
-  <si>
-    <t>녹아웃</t>
-  </si>
-  <si>
-    <t>애티튜드</t>
-  </si>
-  <si>
-    <t>※ 예시 줄은 이 안내 시트에만 있어요. 입력 시트는 빈 상태에서 시작해요.</t>
-  </si>
-  <si>
-    <t>경기코드 (자동)</t>
-  </si>
-  <si>
-    <t>요일 (자동)</t>
-  </si>
-  <si>
-    <t>확인 (자동)</t>
-  </si>
-  <si>
-    <t>7세트 종류</t>
-  </si>
-  <si>
-    <t>7세트 맵</t>
-  </si>
-  <si>
-    <t>8세트 종류</t>
-  </si>
-  <si>
-    <t>8세트 맵</t>
-  </si>
-  <si>
-    <t>팀 이름</t>
-  </si>
-  <si>
-    <t>맵</t>
-  </si>
-  <si>
-    <t>세트 종류 (정규)</t>
-  </si>
-  <si>
-    <t>세트 종류 (플레이오프)</t>
-  </si>
-  <si>
-    <t>이 시트 쓰는 법</t>
-  </si>
-  <si>
-    <t>• A열 팀 이름: 이번 시즌 팀 이름을 먼저 적어 주세요. 사이트 'PL 관리 › 팀 · 선수단'에 등록한 이름과 글자 하나까지 똑같아야 해요.</t>
-  </si>
-  <si>
-    <t>• B열 맵: 지금은 지난 시즌 맵이 예시로 들어 있어요. 이번 시즌 맵풀로 바꿔 주세요 (사이트 '맵풀'과 같은 이름).</t>
-  </si>
-  <si>
-    <t>• C · D열 세트 종류는 고정 값이라 고치지 마세요.</t>
-  </si>
-  <si>
-    <t>• 여기 적은 팀 · 맵이 '정규라운드' · '플레이오프' 시트의 드롭다운 목록이 돼요.</t>
-  </si>
-  <si>
-    <t>팀플3</t>
-  </si>
-  <si>
-    <t>옥타곤</t>
-  </si>
-  <si>
-    <t>팀플4</t>
-  </si>
-  <si>
-    <t>폴스타</t>
-  </si>
-  <si>
-    <t>루나</t>
-  </si>
-  <si>
-    <t>어웨이지정</t>
-  </si>
-  <si>
-    <t>헌터리스</t>
-  </si>
-  <si>
-    <t>레퀴엠</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>그 세트 맵. 홈지정 · 어웨이지정 세트는 '지정 티어 개인전을 고르면 쓰는 맵'을 적어요 (생컨을 고르면 폴리포이드로 자동).</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1173,60 +1175,60 @@
         <v>20</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>21</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>23</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="2:19" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="2:19" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="2:19" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="2:19" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="2:19" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -1240,110 +1242,110 @@
         <v>16</v>
       </c>
       <c r="E24" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="H24" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="I24" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="H24" s="6" t="s">
+      <c r="J24" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="I24" s="6" t="s">
+      <c r="K24" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="J24" s="6" t="s">
+      <c r="L24" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="K24" s="6" t="s">
+      <c r="M24" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="L24" s="6" t="s">
+      <c r="N24" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="M24" s="6" t="s">
+      <c r="O24" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="N24" s="6" t="s">
+      <c r="P24" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="O24" s="6" t="s">
+      <c r="Q24" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="P24" s="6" t="s">
+      <c r="R24" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="Q24" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="R24" s="6" t="s">
-        <v>48</v>
-      </c>
       <c r="S24" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B25" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C25" s="7">
         <v>1</v>
       </c>
       <c r="D25" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F25" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="G25" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="H25" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="G25" s="7" t="s">
+      <c r="I25" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H25" s="7" t="s">
+      <c r="J25" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="I25" s="7" t="s">
+      <c r="K25" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="J25" s="7" t="s">
+      <c r="L25" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="K25" s="7" t="s">
+      <c r="M25" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="L25" s="7" t="s">
+      <c r="N25" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="M25" s="7" t="s">
+      <c r="O25" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="N25" s="7" t="s">
+      <c r="P25" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="O25" s="7" t="s">
+      <c r="Q25" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="P25" s="7" t="s">
+      <c r="R25" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="Q25" s="7" t="s">
+      <c r="S25" s="7" t="s">
         <v>63</v>
-      </c>
-      <c r="R25" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="S25" s="7" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="27" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B27" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1392,67 +1394,67 @@
         <v>16</v>
       </c>
       <c r="D1" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="G1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="K1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="N1" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="P1" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="P1" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q1" s="8" t="s">
-        <v>48</v>
-      </c>
       <c r="R1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="S1" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="T1" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="T1" s="9" t="s">
+      <c r="U1" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="U1" s="9" t="s">
-        <v>30</v>
-      </c>
       <c r="V1" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="W1" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="X1" s="10" t="s">
         <v>67</v>
-      </c>
-      <c r="W1" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="X1" s="10" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
@@ -4351,79 +4353,79 @@
         <v>16</v>
       </c>
       <c r="D1" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="G1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="K1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="N1" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="P1" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="P1" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q1" s="8" t="s">
-        <v>48</v>
-      </c>
       <c r="R1" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="S1" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="T1" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="S1" s="8" t="s">
+      <c r="U1" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="T1" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="U1" s="8" t="s">
-        <v>73</v>
-      </c>
       <c r="V1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="W1" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="W1" s="9" t="s">
+      <c r="X1" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="X1" s="9" t="s">
+      <c r="Y1" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="Y1" s="9" t="s">
-        <v>30</v>
-      </c>
       <c r="Z1" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA1" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB1" s="10" t="s">
         <v>67</v>
-      </c>
-      <c r="AA1" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="AB1" s="10" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.3">
@@ -7612,154 +7614,154 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="F1" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="17"/>
       <c r="B2" s="17" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F2" s="19" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="17"/>
       <c r="B3" s="17" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="17"/>
       <c r="B5" s="17" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="17"/>
       <c r="B6" s="17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="17"/>
       <c r="B7" s="17" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="17"/>
       <c r="B8" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="17"/>
       <c r="B9" s="17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="17"/>
       <c r="B10" s="17" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="17"/>
       <c r="B11" s="17" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="17"/>
       <c r="B12" s="17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="17"/>
       <c r="B13" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">

--- a/public/templates/TFPL_schedule_template.xlsx
+++ b/public/templates/TFPL_schedule_template.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">정규라운드!$A$1:$X$81</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">플레이오프!$A$1:$AB$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">플레이오프!$A$1:$X$81</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
@@ -209,7 +209,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V1" authorId="0">
+    <comment ref="R1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -223,7 +223,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W1" authorId="0">
+    <comment ref="S1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -237,7 +237,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X1" authorId="0">
+    <comment ref="T1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -251,7 +251,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB1" authorId="0">
+    <comment ref="X1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -270,7 +270,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="87">
   <si>
     <t>TFPL 경기 일정 입력 양식</t>
   </si>
@@ -296,9 +296,6 @@
     <t>3. 플레이오프 시트</t>
   </si>
   <si>
-    <t>PO 경기와 결승. 세트가 8개 + 에결. 결승은 매치번호를 비워 두세요.</t>
-  </si>
-  <si>
     <t>4. 확인 칸</t>
   </si>
   <si>
@@ -341,9 +338,6 @@
     <t>에결 맵</t>
   </si>
   <si>
-    <t>7세트(플레이오프는 9세트) ACE 결정전 맵. 3:3(플레이오프 4:4)일 때만 해요.</t>
-  </si>
-  <si>
     <t>시간 (선택)</t>
   </si>
   <si>
@@ -476,18 +470,6 @@
     <t>확인 (자동)</t>
   </si>
   <si>
-    <t>7세트 종류</t>
-  </si>
-  <si>
-    <t>7세트 맵</t>
-  </si>
-  <si>
-    <t>8세트 종류</t>
-  </si>
-  <si>
-    <t>8세트 맵</t>
-  </si>
-  <si>
     <t>팀 이름</t>
   </si>
   <si>
@@ -539,14 +521,21 @@
     <t>레퀴엠</t>
   </si>
   <si>
-    <t>1티어 · 2티어 · 3티어 · 4티어 = 그 티어 선수만 나가는 개인전
+    <t>PO 경기와 결승. 정규와 같이 세트 6개 + 에결 (개인전 4 · 팀플 2, 홈지정 없음). 결승은 매치번호를 비워 두세요.</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>1티어 · 2티어 · 3티어 · 4티어 = 그 티어와 아래 티어 선수가 나가는 개인전
 팀플2 · 팀플3 · 팀플4 = 2:2 · 3:3 · 4:4 (팀플은 인원까지 꼭 구분)
-홈지정 = 홈팀이 지정 티어 개인전(1~4티어 중 선택) 또는 생컨(2:2 · 폴리포이드 · 티어합 지정) 중에서 고르는 세트
-어웨이지정 = 원정팀이 고르는 세트 (플레이오프만)</t>
+홈지정 = 홈팀이 지정 티어 개인전(1~4티어 중 선택) 또는 생컨(2:2 · 폴리포이드 · 티어합 지정) 중에서 고르는 세트 (정규 라운드만)</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>그 세트 맵. 홈지정 · 어웨이지정 세트는 '지정 티어 개인전을 고르면 쓰는 맵'을 적어요 (생컨을 고르면 폴리포이드로 자동).</t>
+    <t>그 세트 맵. 홈지정 세트는 '지정 티어 개인전을 고르면 쓰는 맵'을 적어요 (생컨을 고르면 폴리포이드로 자동).</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>7세트 ACE 결정전 맵 (정규 · 플레이오프 모두). 3:3일 때만 하고, 티어는 경기 당일 핀볼 추첨이에요.</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1122,230 +1111,230 @@
         <v>7</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>9</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>12</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="13" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="14" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>18</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="15" spans="2:3" ht="78" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="2:19" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="2:19" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="2:19" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="2:19" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="2:19" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="2:19" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E24" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="H24" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="I24" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H24" s="6" t="s">
+      <c r="J24" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="I24" s="6" t="s">
+      <c r="K24" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J24" s="6" t="s">
+      <c r="L24" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="K24" s="6" t="s">
+      <c r="M24" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="L24" s="6" t="s">
+      <c r="N24" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="M24" s="6" t="s">
+      <c r="O24" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="N24" s="6" t="s">
+      <c r="P24" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="O24" s="6" t="s">
+      <c r="Q24" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="P24" s="6" t="s">
+      <c r="R24" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="Q24" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="R24" s="6" t="s">
-        <v>46</v>
-      </c>
       <c r="S24" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B25" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C25" s="7">
         <v>1</v>
       </c>
       <c r="D25" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F25" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="G25" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="H25" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="G25" s="7" t="s">
+      <c r="I25" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="H25" s="7" t="s">
+      <c r="J25" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="I25" s="7" t="s">
+      <c r="K25" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="J25" s="7" t="s">
+      <c r="L25" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="K25" s="7" t="s">
+      <c r="M25" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="L25" s="7" t="s">
+      <c r="N25" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="M25" s="7" t="s">
+      <c r="O25" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="N25" s="7" t="s">
+      <c r="P25" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="O25" s="7" t="s">
+      <c r="Q25" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="P25" s="7" t="s">
+      <c r="R25" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="Q25" s="7" t="s">
+      <c r="S25" s="7" t="s">
         <v>61</v>
-      </c>
-      <c r="R25" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="S25" s="7" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="27" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B27" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1385,76 +1374,76 @@
   <sheetData>
     <row r="1" spans="1:24" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D1" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="G1" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="K1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="N1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="P1" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="P1" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q1" s="8" t="s">
-        <v>46</v>
-      </c>
       <c r="R1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="S1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="T1" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="T1" s="9" t="s">
+      <c r="U1" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="U1" s="9" t="s">
-        <v>28</v>
-      </c>
       <c r="V1" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="W1" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="X1" s="10" t="s">
         <v>65</v>
-      </c>
-      <c r="W1" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="X1" s="10" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
@@ -4312,7 +4301,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB81"/>
+  <dimension ref="A1:X81"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="9" customWidth="1"/>
@@ -4329,106 +4318,90 @@
     <col min="14" max="14" width="11" customWidth="1"/>
     <col min="15" max="15" width="13" customWidth="1"/>
     <col min="16" max="16" width="11" customWidth="1"/>
-    <col min="17" max="17" width="13" customWidth="1"/>
-    <col min="18" max="18" width="11" customWidth="1"/>
-    <col min="19" max="19" width="13" customWidth="1"/>
-    <col min="20" max="20" width="11" customWidth="1"/>
-    <col min="21" max="22" width="13" customWidth="1"/>
-    <col min="23" max="23" width="10" customWidth="1"/>
-    <col min="24" max="24" width="16" customWidth="1"/>
-    <col min="25" max="25" width="20" customWidth="1"/>
-    <col min="26" max="26" width="12" customWidth="1"/>
-    <col min="27" max="27" width="9" customWidth="1"/>
-    <col min="28" max="28" width="14" customWidth="1"/>
+    <col min="17" max="18" width="13" customWidth="1"/>
+    <col min="19" max="19" width="10" customWidth="1"/>
+    <col min="20" max="20" width="16" customWidth="1"/>
+    <col min="21" max="21" width="20" customWidth="1"/>
+    <col min="22" max="22" width="12" customWidth="1"/>
+    <col min="23" max="23" width="9" customWidth="1"/>
+    <col min="24" max="24" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D1" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="G1" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="K1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="N1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="P1" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="P1" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q1" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="R1" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="S1" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="T1" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="U1" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="V1" s="6" t="s">
+      <c r="R1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="S1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="W1" s="9" t="s">
+      <c r="T1" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="X1" s="9" t="s">
+      <c r="U1" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="Y1" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z1" s="10" t="s">
+      <c r="V1" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="W1" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="X1" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="AA1" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="AB1" s="10" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="11"/>
@@ -4446,28 +4419,24 @@
       <c r="O2" s="12"/>
       <c r="P2" s="7"/>
       <c r="Q2" s="7"/>
-      <c r="R2" s="12"/>
-      <c r="S2" s="12"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
-      <c r="V2" s="7"/>
-      <c r="W2" s="13"/>
-      <c r="X2" s="14"/>
-      <c r="Y2" s="15"/>
-      <c r="Z2" s="16" t="str">
-        <f t="shared" ref="Z2:Z33" si="0">IF(A2="","",IF(A2="결승","PO-FINAL",IF(B2="","번호 없음",IF(A2="PO","PO-"&amp;B2&amp;"M",A2&amp;"-"&amp;B2&amp;"M"))))</f>
-        <v/>
-      </c>
-      <c r="AA2" s="16" t="str">
-        <f t="shared" ref="AA2:AA33" si="1">IF(C2="","",IFERROR(CHOOSE(WEEKDAY(C2),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
-        <v/>
-      </c>
-      <c r="AB2" s="16" t="str">
-        <f t="shared" ref="AB2:AB33" si="2">IF(COUNTA(A2:V2)=0,"",IF(COUNTBLANK(A2:V2)-IF(A2="결승",IF(B2="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A2:V2)-IF(A2="결승",IF(B2="",1,0),0))&amp;"개",IF(D2=E2,"홈·원정 같음","OK")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R2" s="7"/>
+      <c r="S2" s="13"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="15"/>
+      <c r="V2" s="16" t="str">
+        <f>IF(A2="","",IF(A2="결승","PO-FINAL",IF(B2="","번호 없음",IF(A2="PO","PO-"&amp;B2&amp;"M",A2&amp;"-"&amp;B2&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W2" s="16" t="str">
+        <f>IF(C2="","",IFERROR(CHOOSE(WEEKDAY(C2),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X2" s="16" t="str">
+        <f>IF(COUNTA(A2:R2)=0,"",IF(COUNTBLANK(A2:R2)-IF(A2="결승",IF(B2="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A2:R2)-IF(A2="결승",IF(B2="",1,0),0))&amp;"개",IF(D2=E2,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
       <c r="C3" s="11"/>
@@ -4485,28 +4454,24 @@
       <c r="O3" s="12"/>
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
-      <c r="R3" s="12"/>
-      <c r="S3" s="12"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7"/>
-      <c r="V3" s="7"/>
-      <c r="W3" s="13"/>
-      <c r="X3" s="14"/>
-      <c r="Y3" s="15"/>
-      <c r="Z3" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA3" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB3" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R3" s="7"/>
+      <c r="S3" s="13"/>
+      <c r="T3" s="14"/>
+      <c r="U3" s="15"/>
+      <c r="V3" s="16" t="str">
+        <f>IF(A3="","",IF(A3="결승","PO-FINAL",IF(B3="","번호 없음",IF(A3="PO","PO-"&amp;B3&amp;"M",A3&amp;"-"&amp;B3&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W3" s="16" t="str">
+        <f>IF(C3="","",IFERROR(CHOOSE(WEEKDAY(C3),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X3" s="16" t="str">
+        <f>IF(COUNTA(A3:R3)=0,"",IF(COUNTBLANK(A3:R3)-IF(A3="결승",IF(B3="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A3:R3)-IF(A3="결승",IF(B3="",1,0),0))&amp;"개",IF(D3=E3,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="11"/>
@@ -4524,28 +4489,24 @@
       <c r="O4" s="12"/>
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
-      <c r="R4" s="12"/>
-      <c r="S4" s="12"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
-      <c r="W4" s="13"/>
-      <c r="X4" s="14"/>
-      <c r="Y4" s="15"/>
-      <c r="Z4" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA4" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB4" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R4" s="7"/>
+      <c r="S4" s="13"/>
+      <c r="T4" s="14"/>
+      <c r="U4" s="15"/>
+      <c r="V4" s="16" t="str">
+        <f>IF(A4="","",IF(A4="결승","PO-FINAL",IF(B4="","번호 없음",IF(A4="PO","PO-"&amp;B4&amp;"M",A4&amp;"-"&amp;B4&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W4" s="16" t="str">
+        <f>IF(C4="","",IFERROR(CHOOSE(WEEKDAY(C4),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X4" s="16" t="str">
+        <f>IF(COUNTA(A4:R4)=0,"",IF(COUNTBLANK(A4:R4)-IF(A4="결승",IF(B4="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A4:R4)-IF(A4="결승",IF(B4="",1,0),0))&amp;"개",IF(D4=E4,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="11"/>
@@ -4563,28 +4524,24 @@
       <c r="O5" s="12"/>
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
-      <c r="R5" s="12"/>
-      <c r="S5" s="12"/>
-      <c r="T5" s="7"/>
-      <c r="U5" s="7"/>
-      <c r="V5" s="7"/>
-      <c r="W5" s="13"/>
-      <c r="X5" s="14"/>
-      <c r="Y5" s="15"/>
-      <c r="Z5" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA5" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB5" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R5" s="7"/>
+      <c r="S5" s="13"/>
+      <c r="T5" s="14"/>
+      <c r="U5" s="15"/>
+      <c r="V5" s="16" t="str">
+        <f>IF(A5="","",IF(A5="결승","PO-FINAL",IF(B5="","번호 없음",IF(A5="PO","PO-"&amp;B5&amp;"M",A5&amp;"-"&amp;B5&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W5" s="16" t="str">
+        <f>IF(C5="","",IFERROR(CHOOSE(WEEKDAY(C5),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X5" s="16" t="str">
+        <f>IF(COUNTA(A5:R5)=0,"",IF(COUNTBLANK(A5:R5)-IF(A5="결승",IF(B5="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A5:R5)-IF(A5="결승",IF(B5="",1,0),0))&amp;"개",IF(D5=E5,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="11"/>
@@ -4602,28 +4559,24 @@
       <c r="O6" s="12"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
-      <c r="R6" s="12"/>
-      <c r="S6" s="12"/>
-      <c r="T6" s="7"/>
-      <c r="U6" s="7"/>
-      <c r="V6" s="7"/>
-      <c r="W6" s="13"/>
-      <c r="X6" s="14"/>
-      <c r="Y6" s="15"/>
-      <c r="Z6" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA6" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB6" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R6" s="7"/>
+      <c r="S6" s="13"/>
+      <c r="T6" s="14"/>
+      <c r="U6" s="15"/>
+      <c r="V6" s="16" t="str">
+        <f>IF(A6="","",IF(A6="결승","PO-FINAL",IF(B6="","번호 없음",IF(A6="PO","PO-"&amp;B6&amp;"M",A6&amp;"-"&amp;B6&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W6" s="16" t="str">
+        <f>IF(C6="","",IFERROR(CHOOSE(WEEKDAY(C6),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X6" s="16" t="str">
+        <f>IF(COUNTA(A6:R6)=0,"",IF(COUNTBLANK(A6:R6)-IF(A6="결승",IF(B6="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A6:R6)-IF(A6="결승",IF(B6="",1,0),0))&amp;"개",IF(D6=E6,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="11"/>
@@ -4641,28 +4594,24 @@
       <c r="O7" s="12"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
-      <c r="R7" s="12"/>
-      <c r="S7" s="12"/>
-      <c r="T7" s="7"/>
-      <c r="U7" s="7"/>
-      <c r="V7" s="7"/>
-      <c r="W7" s="13"/>
-      <c r="X7" s="14"/>
-      <c r="Y7" s="15"/>
-      <c r="Z7" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA7" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB7" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R7" s="7"/>
+      <c r="S7" s="13"/>
+      <c r="T7" s="14"/>
+      <c r="U7" s="15"/>
+      <c r="V7" s="16" t="str">
+        <f>IF(A7="","",IF(A7="결승","PO-FINAL",IF(B7="","번호 없음",IF(A7="PO","PO-"&amp;B7&amp;"M",A7&amp;"-"&amp;B7&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W7" s="16" t="str">
+        <f>IF(C7="","",IFERROR(CHOOSE(WEEKDAY(C7),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X7" s="16" t="str">
+        <f>IF(COUNTA(A7:R7)=0,"",IF(COUNTBLANK(A7:R7)-IF(A7="결승",IF(B7="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A7:R7)-IF(A7="결승",IF(B7="",1,0),0))&amp;"개",IF(D7=E7,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="11"/>
@@ -4680,28 +4629,24 @@
       <c r="O8" s="12"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
-      <c r="R8" s="12"/>
-      <c r="S8" s="12"/>
-      <c r="T8" s="7"/>
-      <c r="U8" s="7"/>
-      <c r="V8" s="7"/>
-      <c r="W8" s="13"/>
-      <c r="X8" s="14"/>
-      <c r="Y8" s="15"/>
-      <c r="Z8" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA8" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB8" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R8" s="7"/>
+      <c r="S8" s="13"/>
+      <c r="T8" s="14"/>
+      <c r="U8" s="15"/>
+      <c r="V8" s="16" t="str">
+        <f>IF(A8="","",IF(A8="결승","PO-FINAL",IF(B8="","번호 없음",IF(A8="PO","PO-"&amp;B8&amp;"M",A8&amp;"-"&amp;B8&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W8" s="16" t="str">
+        <f>IF(C8="","",IFERROR(CHOOSE(WEEKDAY(C8),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X8" s="16" t="str">
+        <f>IF(COUNTA(A8:R8)=0,"",IF(COUNTBLANK(A8:R8)-IF(A8="결승",IF(B8="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A8:R8)-IF(A8="결승",IF(B8="",1,0),0))&amp;"개",IF(D8=E8,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="11"/>
@@ -4719,28 +4664,24 @@
       <c r="O9" s="12"/>
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
-      <c r="R9" s="12"/>
-      <c r="S9" s="12"/>
-      <c r="T9" s="7"/>
-      <c r="U9" s="7"/>
-      <c r="V9" s="7"/>
-      <c r="W9" s="13"/>
-      <c r="X9" s="14"/>
-      <c r="Y9" s="15"/>
-      <c r="Z9" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA9" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB9" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R9" s="7"/>
+      <c r="S9" s="13"/>
+      <c r="T9" s="14"/>
+      <c r="U9" s="15"/>
+      <c r="V9" s="16" t="str">
+        <f>IF(A9="","",IF(A9="결승","PO-FINAL",IF(B9="","번호 없음",IF(A9="PO","PO-"&amp;B9&amp;"M",A9&amp;"-"&amp;B9&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W9" s="16" t="str">
+        <f>IF(C9="","",IFERROR(CHOOSE(WEEKDAY(C9),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X9" s="16" t="str">
+        <f>IF(COUNTA(A9:R9)=0,"",IF(COUNTBLANK(A9:R9)-IF(A9="결승",IF(B9="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A9:R9)-IF(A9="결승",IF(B9="",1,0),0))&amp;"개",IF(D9=E9,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="11"/>
@@ -4758,28 +4699,24 @@
       <c r="O10" s="12"/>
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
-      <c r="T10" s="7"/>
-      <c r="U10" s="7"/>
-      <c r="V10" s="7"/>
-      <c r="W10" s="13"/>
-      <c r="X10" s="14"/>
-      <c r="Y10" s="15"/>
-      <c r="Z10" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA10" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB10" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R10" s="7"/>
+      <c r="S10" s="13"/>
+      <c r="T10" s="14"/>
+      <c r="U10" s="15"/>
+      <c r="V10" s="16" t="str">
+        <f>IF(A10="","",IF(A10="결승","PO-FINAL",IF(B10="","번호 없음",IF(A10="PO","PO-"&amp;B10&amp;"M",A10&amp;"-"&amp;B10&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W10" s="16" t="str">
+        <f>IF(C10="","",IFERROR(CHOOSE(WEEKDAY(C10),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X10" s="16" t="str">
+        <f>IF(COUNTA(A10:R10)=0,"",IF(COUNTBLANK(A10:R10)-IF(A10="결승",IF(B10="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A10:R10)-IF(A10="결승",IF(B10="",1,0),0))&amp;"개",IF(D10=E10,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="11"/>
@@ -4797,28 +4734,24 @@
       <c r="O11" s="12"/>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
-      <c r="R11" s="12"/>
-      <c r="S11" s="12"/>
-      <c r="T11" s="7"/>
-      <c r="U11" s="7"/>
-      <c r="V11" s="7"/>
-      <c r="W11" s="13"/>
-      <c r="X11" s="14"/>
-      <c r="Y11" s="15"/>
-      <c r="Z11" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA11" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB11" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R11" s="7"/>
+      <c r="S11" s="13"/>
+      <c r="T11" s="14"/>
+      <c r="U11" s="15"/>
+      <c r="V11" s="16" t="str">
+        <f>IF(A11="","",IF(A11="결승","PO-FINAL",IF(B11="","번호 없음",IF(A11="PO","PO-"&amp;B11&amp;"M",A11&amp;"-"&amp;B11&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W11" s="16" t="str">
+        <f>IF(C11="","",IFERROR(CHOOSE(WEEKDAY(C11),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X11" s="16" t="str">
+        <f>IF(COUNTA(A11:R11)=0,"",IF(COUNTBLANK(A11:R11)-IF(A11="결승",IF(B11="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A11:R11)-IF(A11="결승",IF(B11="",1,0),0))&amp;"개",IF(D11=E11,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="11"/>
@@ -4836,28 +4769,24 @@
       <c r="O12" s="12"/>
       <c r="P12" s="7"/>
       <c r="Q12" s="7"/>
-      <c r="R12" s="12"/>
-      <c r="S12" s="12"/>
-      <c r="T12" s="7"/>
-      <c r="U12" s="7"/>
-      <c r="V12" s="7"/>
-      <c r="W12" s="13"/>
-      <c r="X12" s="14"/>
-      <c r="Y12" s="15"/>
-      <c r="Z12" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA12" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB12" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R12" s="7"/>
+      <c r="S12" s="13"/>
+      <c r="T12" s="14"/>
+      <c r="U12" s="15"/>
+      <c r="V12" s="16" t="str">
+        <f>IF(A12="","",IF(A12="결승","PO-FINAL",IF(B12="","번호 없음",IF(A12="PO","PO-"&amp;B12&amp;"M",A12&amp;"-"&amp;B12&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W12" s="16" t="str">
+        <f>IF(C12="","",IFERROR(CHOOSE(WEEKDAY(C12),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X12" s="16" t="str">
+        <f>IF(COUNTA(A12:R12)=0,"",IF(COUNTBLANK(A12:R12)-IF(A12="결승",IF(B12="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A12:R12)-IF(A12="결승",IF(B12="",1,0),0))&amp;"개",IF(D12=E12,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="11"/>
@@ -4875,28 +4804,24 @@
       <c r="O13" s="12"/>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
-      <c r="R13" s="12"/>
-      <c r="S13" s="12"/>
-      <c r="T13" s="7"/>
-      <c r="U13" s="7"/>
-      <c r="V13" s="7"/>
-      <c r="W13" s="13"/>
-      <c r="X13" s="14"/>
-      <c r="Y13" s="15"/>
-      <c r="Z13" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA13" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB13" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R13" s="7"/>
+      <c r="S13" s="13"/>
+      <c r="T13" s="14"/>
+      <c r="U13" s="15"/>
+      <c r="V13" s="16" t="str">
+        <f>IF(A13="","",IF(A13="결승","PO-FINAL",IF(B13="","번호 없음",IF(A13="PO","PO-"&amp;B13&amp;"M",A13&amp;"-"&amp;B13&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W13" s="16" t="str">
+        <f>IF(C13="","",IFERROR(CHOOSE(WEEKDAY(C13),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X13" s="16" t="str">
+        <f>IF(COUNTA(A13:R13)=0,"",IF(COUNTBLANK(A13:R13)-IF(A13="결승",IF(B13="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A13:R13)-IF(A13="결승",IF(B13="",1,0),0))&amp;"개",IF(D13=E13,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="11"/>
@@ -4914,28 +4839,24 @@
       <c r="O14" s="12"/>
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
-      <c r="R14" s="12"/>
-      <c r="S14" s="12"/>
-      <c r="T14" s="7"/>
-      <c r="U14" s="7"/>
-      <c r="V14" s="7"/>
-      <c r="W14" s="13"/>
-      <c r="X14" s="14"/>
-      <c r="Y14" s="15"/>
-      <c r="Z14" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA14" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB14" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R14" s="7"/>
+      <c r="S14" s="13"/>
+      <c r="T14" s="14"/>
+      <c r="U14" s="15"/>
+      <c r="V14" s="16" t="str">
+        <f>IF(A14="","",IF(A14="결승","PO-FINAL",IF(B14="","번호 없음",IF(A14="PO","PO-"&amp;B14&amp;"M",A14&amp;"-"&amp;B14&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W14" s="16" t="str">
+        <f>IF(C14="","",IFERROR(CHOOSE(WEEKDAY(C14),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X14" s="16" t="str">
+        <f>IF(COUNTA(A14:R14)=0,"",IF(COUNTBLANK(A14:R14)-IF(A14="결승",IF(B14="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A14:R14)-IF(A14="결승",IF(B14="",1,0),0))&amp;"개",IF(D14=E14,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="11"/>
@@ -4953,28 +4874,24 @@
       <c r="O15" s="12"/>
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
-      <c r="R15" s="12"/>
-      <c r="S15" s="12"/>
-      <c r="T15" s="7"/>
-      <c r="U15" s="7"/>
-      <c r="V15" s="7"/>
-      <c r="W15" s="13"/>
-      <c r="X15" s="14"/>
-      <c r="Y15" s="15"/>
-      <c r="Z15" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA15" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB15" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R15" s="7"/>
+      <c r="S15" s="13"/>
+      <c r="T15" s="14"/>
+      <c r="U15" s="15"/>
+      <c r="V15" s="16" t="str">
+        <f>IF(A15="","",IF(A15="결승","PO-FINAL",IF(B15="","번호 없음",IF(A15="PO","PO-"&amp;B15&amp;"M",A15&amp;"-"&amp;B15&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W15" s="16" t="str">
+        <f>IF(C15="","",IFERROR(CHOOSE(WEEKDAY(C15),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X15" s="16" t="str">
+        <f>IF(COUNTA(A15:R15)=0,"",IF(COUNTBLANK(A15:R15)-IF(A15="결승",IF(B15="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A15:R15)-IF(A15="결승",IF(B15="",1,0),0))&amp;"개",IF(D15=E15,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="11"/>
@@ -4992,28 +4909,24 @@
       <c r="O16" s="12"/>
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
-      <c r="R16" s="12"/>
-      <c r="S16" s="12"/>
-      <c r="T16" s="7"/>
-      <c r="U16" s="7"/>
-      <c r="V16" s="7"/>
-      <c r="W16" s="13"/>
-      <c r="X16" s="14"/>
-      <c r="Y16" s="15"/>
-      <c r="Z16" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA16" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB16" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R16" s="7"/>
+      <c r="S16" s="13"/>
+      <c r="T16" s="14"/>
+      <c r="U16" s="15"/>
+      <c r="V16" s="16" t="str">
+        <f>IF(A16="","",IF(A16="결승","PO-FINAL",IF(B16="","번호 없음",IF(A16="PO","PO-"&amp;B16&amp;"M",A16&amp;"-"&amp;B16&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W16" s="16" t="str">
+        <f>IF(C16="","",IFERROR(CHOOSE(WEEKDAY(C16),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X16" s="16" t="str">
+        <f>IF(COUNTA(A16:R16)=0,"",IF(COUNTBLANK(A16:R16)-IF(A16="결승",IF(B16="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A16:R16)-IF(A16="결승",IF(B16="",1,0),0))&amp;"개",IF(D16=E16,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="11"/>
@@ -5031,28 +4944,24 @@
       <c r="O17" s="12"/>
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
-      <c r="R17" s="12"/>
-      <c r="S17" s="12"/>
-      <c r="T17" s="7"/>
-      <c r="U17" s="7"/>
-      <c r="V17" s="7"/>
-      <c r="W17" s="13"/>
-      <c r="X17" s="14"/>
-      <c r="Y17" s="15"/>
-      <c r="Z17" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA17" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB17" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R17" s="7"/>
+      <c r="S17" s="13"/>
+      <c r="T17" s="14"/>
+      <c r="U17" s="15"/>
+      <c r="V17" s="16" t="str">
+        <f>IF(A17="","",IF(A17="결승","PO-FINAL",IF(B17="","번호 없음",IF(A17="PO","PO-"&amp;B17&amp;"M",A17&amp;"-"&amp;B17&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W17" s="16" t="str">
+        <f>IF(C17="","",IFERROR(CHOOSE(WEEKDAY(C17),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X17" s="16" t="str">
+        <f>IF(COUNTA(A17:R17)=0,"",IF(COUNTBLANK(A17:R17)-IF(A17="결승",IF(B17="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A17:R17)-IF(A17="결승",IF(B17="",1,0),0))&amp;"개",IF(D17=E17,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="11"/>
@@ -5070,28 +4979,24 @@
       <c r="O18" s="12"/>
       <c r="P18" s="7"/>
       <c r="Q18" s="7"/>
-      <c r="R18" s="12"/>
-      <c r="S18" s="12"/>
-      <c r="T18" s="7"/>
-      <c r="U18" s="7"/>
-      <c r="V18" s="7"/>
-      <c r="W18" s="13"/>
-      <c r="X18" s="14"/>
-      <c r="Y18" s="15"/>
-      <c r="Z18" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA18" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB18" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R18" s="7"/>
+      <c r="S18" s="13"/>
+      <c r="T18" s="14"/>
+      <c r="U18" s="15"/>
+      <c r="V18" s="16" t="str">
+        <f>IF(A18="","",IF(A18="결승","PO-FINAL",IF(B18="","번호 없음",IF(A18="PO","PO-"&amp;B18&amp;"M",A18&amp;"-"&amp;B18&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W18" s="16" t="str">
+        <f>IF(C18="","",IFERROR(CHOOSE(WEEKDAY(C18),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X18" s="16" t="str">
+        <f>IF(COUNTA(A18:R18)=0,"",IF(COUNTBLANK(A18:R18)-IF(A18="결승",IF(B18="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A18:R18)-IF(A18="결승",IF(B18="",1,0),0))&amp;"개",IF(D18=E18,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="11"/>
@@ -5109,28 +5014,24 @@
       <c r="O19" s="12"/>
       <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
-      <c r="R19" s="12"/>
-      <c r="S19" s="12"/>
-      <c r="T19" s="7"/>
-      <c r="U19" s="7"/>
-      <c r="V19" s="7"/>
-      <c r="W19" s="13"/>
-      <c r="X19" s="14"/>
-      <c r="Y19" s="15"/>
-      <c r="Z19" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA19" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB19" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R19" s="7"/>
+      <c r="S19" s="13"/>
+      <c r="T19" s="14"/>
+      <c r="U19" s="15"/>
+      <c r="V19" s="16" t="str">
+        <f>IF(A19="","",IF(A19="결승","PO-FINAL",IF(B19="","번호 없음",IF(A19="PO","PO-"&amp;B19&amp;"M",A19&amp;"-"&amp;B19&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W19" s="16" t="str">
+        <f>IF(C19="","",IFERROR(CHOOSE(WEEKDAY(C19),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X19" s="16" t="str">
+        <f>IF(COUNTA(A19:R19)=0,"",IF(COUNTBLANK(A19:R19)-IF(A19="결승",IF(B19="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A19:R19)-IF(A19="결승",IF(B19="",1,0),0))&amp;"개",IF(D19=E19,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="11"/>
@@ -5148,28 +5049,24 @@
       <c r="O20" s="12"/>
       <c r="P20" s="7"/>
       <c r="Q20" s="7"/>
-      <c r="R20" s="12"/>
-      <c r="S20" s="12"/>
-      <c r="T20" s="7"/>
-      <c r="U20" s="7"/>
-      <c r="V20" s="7"/>
-      <c r="W20" s="13"/>
-      <c r="X20" s="14"/>
-      <c r="Y20" s="15"/>
-      <c r="Z20" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA20" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB20" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R20" s="7"/>
+      <c r="S20" s="13"/>
+      <c r="T20" s="14"/>
+      <c r="U20" s="15"/>
+      <c r="V20" s="16" t="str">
+        <f>IF(A20="","",IF(A20="결승","PO-FINAL",IF(B20="","번호 없음",IF(A20="PO","PO-"&amp;B20&amp;"M",A20&amp;"-"&amp;B20&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W20" s="16" t="str">
+        <f>IF(C20="","",IFERROR(CHOOSE(WEEKDAY(C20),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X20" s="16" t="str">
+        <f>IF(COUNTA(A20:R20)=0,"",IF(COUNTBLANK(A20:R20)-IF(A20="결승",IF(B20="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A20:R20)-IF(A20="결승",IF(B20="",1,0),0))&amp;"개",IF(D20=E20,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="11"/>
@@ -5187,28 +5084,24 @@
       <c r="O21" s="12"/>
       <c r="P21" s="7"/>
       <c r="Q21" s="7"/>
-      <c r="R21" s="12"/>
-      <c r="S21" s="12"/>
-      <c r="T21" s="7"/>
-      <c r="U21" s="7"/>
-      <c r="V21" s="7"/>
-      <c r="W21" s="13"/>
-      <c r="X21" s="14"/>
-      <c r="Y21" s="15"/>
-      <c r="Z21" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA21" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB21" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R21" s="7"/>
+      <c r="S21" s="13"/>
+      <c r="T21" s="14"/>
+      <c r="U21" s="15"/>
+      <c r="V21" s="16" t="str">
+        <f>IF(A21="","",IF(A21="결승","PO-FINAL",IF(B21="","번호 없음",IF(A21="PO","PO-"&amp;B21&amp;"M",A21&amp;"-"&amp;B21&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W21" s="16" t="str">
+        <f>IF(C21="","",IFERROR(CHOOSE(WEEKDAY(C21),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X21" s="16" t="str">
+        <f>IF(COUNTA(A21:R21)=0,"",IF(COUNTBLANK(A21:R21)-IF(A21="결승",IF(B21="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A21:R21)-IF(A21="결승",IF(B21="",1,0),0))&amp;"개",IF(D21=E21,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="11"/>
@@ -5226,28 +5119,24 @@
       <c r="O22" s="12"/>
       <c r="P22" s="7"/>
       <c r="Q22" s="7"/>
-      <c r="R22" s="12"/>
-      <c r="S22" s="12"/>
-      <c r="T22" s="7"/>
-      <c r="U22" s="7"/>
-      <c r="V22" s="7"/>
-      <c r="W22" s="13"/>
-      <c r="X22" s="14"/>
-      <c r="Y22" s="15"/>
-      <c r="Z22" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA22" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB22" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R22" s="7"/>
+      <c r="S22" s="13"/>
+      <c r="T22" s="14"/>
+      <c r="U22" s="15"/>
+      <c r="V22" s="16" t="str">
+        <f>IF(A22="","",IF(A22="결승","PO-FINAL",IF(B22="","번호 없음",IF(A22="PO","PO-"&amp;B22&amp;"M",A22&amp;"-"&amp;B22&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W22" s="16" t="str">
+        <f>IF(C22="","",IFERROR(CHOOSE(WEEKDAY(C22),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X22" s="16" t="str">
+        <f>IF(COUNTA(A22:R22)=0,"",IF(COUNTBLANK(A22:R22)-IF(A22="결승",IF(B22="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A22:R22)-IF(A22="결승",IF(B22="",1,0),0))&amp;"개",IF(D22=E22,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="11"/>
@@ -5265,28 +5154,24 @@
       <c r="O23" s="12"/>
       <c r="P23" s="7"/>
       <c r="Q23" s="7"/>
-      <c r="R23" s="12"/>
-      <c r="S23" s="12"/>
-      <c r="T23" s="7"/>
-      <c r="U23" s="7"/>
-      <c r="V23" s="7"/>
-      <c r="W23" s="13"/>
-      <c r="X23" s="14"/>
-      <c r="Y23" s="15"/>
-      <c r="Z23" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA23" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB23" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R23" s="7"/>
+      <c r="S23" s="13"/>
+      <c r="T23" s="14"/>
+      <c r="U23" s="15"/>
+      <c r="V23" s="16" t="str">
+        <f>IF(A23="","",IF(A23="결승","PO-FINAL",IF(B23="","번호 없음",IF(A23="PO","PO-"&amp;B23&amp;"M",A23&amp;"-"&amp;B23&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W23" s="16" t="str">
+        <f>IF(C23="","",IFERROR(CHOOSE(WEEKDAY(C23),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X23" s="16" t="str">
+        <f>IF(COUNTA(A23:R23)=0,"",IF(COUNTBLANK(A23:R23)-IF(A23="결승",IF(B23="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A23:R23)-IF(A23="결승",IF(B23="",1,0),0))&amp;"개",IF(D23=E23,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="11"/>
@@ -5304,28 +5189,24 @@
       <c r="O24" s="12"/>
       <c r="P24" s="7"/>
       <c r="Q24" s="7"/>
-      <c r="R24" s="12"/>
-      <c r="S24" s="12"/>
-      <c r="T24" s="7"/>
-      <c r="U24" s="7"/>
-      <c r="V24" s="7"/>
-      <c r="W24" s="13"/>
-      <c r="X24" s="14"/>
-      <c r="Y24" s="15"/>
-      <c r="Z24" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA24" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB24" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R24" s="7"/>
+      <c r="S24" s="13"/>
+      <c r="T24" s="14"/>
+      <c r="U24" s="15"/>
+      <c r="V24" s="16" t="str">
+        <f>IF(A24="","",IF(A24="결승","PO-FINAL",IF(B24="","번호 없음",IF(A24="PO","PO-"&amp;B24&amp;"M",A24&amp;"-"&amp;B24&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W24" s="16" t="str">
+        <f>IF(C24="","",IFERROR(CHOOSE(WEEKDAY(C24),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X24" s="16" t="str">
+        <f>IF(COUNTA(A24:R24)=0,"",IF(COUNTBLANK(A24:R24)-IF(A24="결승",IF(B24="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A24:R24)-IF(A24="결승",IF(B24="",1,0),0))&amp;"개",IF(D24=E24,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="11"/>
@@ -5343,28 +5224,24 @@
       <c r="O25" s="12"/>
       <c r="P25" s="7"/>
       <c r="Q25" s="7"/>
-      <c r="R25" s="12"/>
-      <c r="S25" s="12"/>
-      <c r="T25" s="7"/>
-      <c r="U25" s="7"/>
-      <c r="V25" s="7"/>
-      <c r="W25" s="13"/>
-      <c r="X25" s="14"/>
-      <c r="Y25" s="15"/>
-      <c r="Z25" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA25" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB25" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R25" s="7"/>
+      <c r="S25" s="13"/>
+      <c r="T25" s="14"/>
+      <c r="U25" s="15"/>
+      <c r="V25" s="16" t="str">
+        <f>IF(A25="","",IF(A25="결승","PO-FINAL",IF(B25="","번호 없음",IF(A25="PO","PO-"&amp;B25&amp;"M",A25&amp;"-"&amp;B25&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W25" s="16" t="str">
+        <f>IF(C25="","",IFERROR(CHOOSE(WEEKDAY(C25),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X25" s="16" t="str">
+        <f>IF(COUNTA(A25:R25)=0,"",IF(COUNTBLANK(A25:R25)-IF(A25="결승",IF(B25="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A25:R25)-IF(A25="결승",IF(B25="",1,0),0))&amp;"개",IF(D25=E25,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="11"/>
@@ -5382,28 +5259,24 @@
       <c r="O26" s="12"/>
       <c r="P26" s="7"/>
       <c r="Q26" s="7"/>
-      <c r="R26" s="12"/>
-      <c r="S26" s="12"/>
-      <c r="T26" s="7"/>
-      <c r="U26" s="7"/>
-      <c r="V26" s="7"/>
-      <c r="W26" s="13"/>
-      <c r="X26" s="14"/>
-      <c r="Y26" s="15"/>
-      <c r="Z26" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA26" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB26" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R26" s="7"/>
+      <c r="S26" s="13"/>
+      <c r="T26" s="14"/>
+      <c r="U26" s="15"/>
+      <c r="V26" s="16" t="str">
+        <f>IF(A26="","",IF(A26="결승","PO-FINAL",IF(B26="","번호 없음",IF(A26="PO","PO-"&amp;B26&amp;"M",A26&amp;"-"&amp;B26&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W26" s="16" t="str">
+        <f>IF(C26="","",IFERROR(CHOOSE(WEEKDAY(C26),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X26" s="16" t="str">
+        <f>IF(COUNTA(A26:R26)=0,"",IF(COUNTBLANK(A26:R26)-IF(A26="결승",IF(B26="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A26:R26)-IF(A26="결승",IF(B26="",1,0),0))&amp;"개",IF(D26=E26,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A27" s="7"/>
       <c r="B27" s="7"/>
       <c r="C27" s="11"/>
@@ -5421,28 +5294,24 @@
       <c r="O27" s="12"/>
       <c r="P27" s="7"/>
       <c r="Q27" s="7"/>
-      <c r="R27" s="12"/>
-      <c r="S27" s="12"/>
-      <c r="T27" s="7"/>
-      <c r="U27" s="7"/>
-      <c r="V27" s="7"/>
-      <c r="W27" s="13"/>
-      <c r="X27" s="14"/>
-      <c r="Y27" s="15"/>
-      <c r="Z27" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA27" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB27" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R27" s="7"/>
+      <c r="S27" s="13"/>
+      <c r="T27" s="14"/>
+      <c r="U27" s="15"/>
+      <c r="V27" s="16" t="str">
+        <f>IF(A27="","",IF(A27="결승","PO-FINAL",IF(B27="","번호 없음",IF(A27="PO","PO-"&amp;B27&amp;"M",A27&amp;"-"&amp;B27&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W27" s="16" t="str">
+        <f>IF(C27="","",IFERROR(CHOOSE(WEEKDAY(C27),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X27" s="16" t="str">
+        <f>IF(COUNTA(A27:R27)=0,"",IF(COUNTBLANK(A27:R27)-IF(A27="결승",IF(B27="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A27:R27)-IF(A27="결승",IF(B27="",1,0),0))&amp;"개",IF(D27=E27,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A28" s="7"/>
       <c r="B28" s="7"/>
       <c r="C28" s="11"/>
@@ -5460,28 +5329,24 @@
       <c r="O28" s="12"/>
       <c r="P28" s="7"/>
       <c r="Q28" s="7"/>
-      <c r="R28" s="12"/>
-      <c r="S28" s="12"/>
-      <c r="T28" s="7"/>
-      <c r="U28" s="7"/>
-      <c r="V28" s="7"/>
-      <c r="W28" s="13"/>
-      <c r="X28" s="14"/>
-      <c r="Y28" s="15"/>
-      <c r="Z28" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA28" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB28" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R28" s="7"/>
+      <c r="S28" s="13"/>
+      <c r="T28" s="14"/>
+      <c r="U28" s="15"/>
+      <c r="V28" s="16" t="str">
+        <f>IF(A28="","",IF(A28="결승","PO-FINAL",IF(B28="","번호 없음",IF(A28="PO","PO-"&amp;B28&amp;"M",A28&amp;"-"&amp;B28&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W28" s="16" t="str">
+        <f>IF(C28="","",IFERROR(CHOOSE(WEEKDAY(C28),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X28" s="16" t="str">
+        <f>IF(COUNTA(A28:R28)=0,"",IF(COUNTBLANK(A28:R28)-IF(A28="결승",IF(B28="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A28:R28)-IF(A28="결승",IF(B28="",1,0),0))&amp;"개",IF(D28=E28,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A29" s="7"/>
       <c r="B29" s="7"/>
       <c r="C29" s="11"/>
@@ -5499,28 +5364,24 @@
       <c r="O29" s="12"/>
       <c r="P29" s="7"/>
       <c r="Q29" s="7"/>
-      <c r="R29" s="12"/>
-      <c r="S29" s="12"/>
-      <c r="T29" s="7"/>
-      <c r="U29" s="7"/>
-      <c r="V29" s="7"/>
-      <c r="W29" s="13"/>
-      <c r="X29" s="14"/>
-      <c r="Y29" s="15"/>
-      <c r="Z29" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA29" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB29" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R29" s="7"/>
+      <c r="S29" s="13"/>
+      <c r="T29" s="14"/>
+      <c r="U29" s="15"/>
+      <c r="V29" s="16" t="str">
+        <f>IF(A29="","",IF(A29="결승","PO-FINAL",IF(B29="","번호 없음",IF(A29="PO","PO-"&amp;B29&amp;"M",A29&amp;"-"&amp;B29&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W29" s="16" t="str">
+        <f>IF(C29="","",IFERROR(CHOOSE(WEEKDAY(C29),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X29" s="16" t="str">
+        <f>IF(COUNTA(A29:R29)=0,"",IF(COUNTBLANK(A29:R29)-IF(A29="결승",IF(B29="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A29:R29)-IF(A29="결승",IF(B29="",1,0),0))&amp;"개",IF(D29=E29,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="11"/>
@@ -5538,28 +5399,24 @@
       <c r="O30" s="12"/>
       <c r="P30" s="7"/>
       <c r="Q30" s="7"/>
-      <c r="R30" s="12"/>
-      <c r="S30" s="12"/>
-      <c r="T30" s="7"/>
-      <c r="U30" s="7"/>
-      <c r="V30" s="7"/>
-      <c r="W30" s="13"/>
-      <c r="X30" s="14"/>
-      <c r="Y30" s="15"/>
-      <c r="Z30" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA30" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB30" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R30" s="7"/>
+      <c r="S30" s="13"/>
+      <c r="T30" s="14"/>
+      <c r="U30" s="15"/>
+      <c r="V30" s="16" t="str">
+        <f>IF(A30="","",IF(A30="결승","PO-FINAL",IF(B30="","번호 없음",IF(A30="PO","PO-"&amp;B30&amp;"M",A30&amp;"-"&amp;B30&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W30" s="16" t="str">
+        <f>IF(C30="","",IFERROR(CHOOSE(WEEKDAY(C30),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X30" s="16" t="str">
+        <f>IF(COUNTA(A30:R30)=0,"",IF(COUNTBLANK(A30:R30)-IF(A30="결승",IF(B30="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A30:R30)-IF(A30="결승",IF(B30="",1,0),0))&amp;"개",IF(D30=E30,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31" s="7"/>
       <c r="B31" s="7"/>
       <c r="C31" s="11"/>
@@ -5577,28 +5434,24 @@
       <c r="O31" s="12"/>
       <c r="P31" s="7"/>
       <c r="Q31" s="7"/>
-      <c r="R31" s="12"/>
-      <c r="S31" s="12"/>
-      <c r="T31" s="7"/>
-      <c r="U31" s="7"/>
-      <c r="V31" s="7"/>
-      <c r="W31" s="13"/>
-      <c r="X31" s="14"/>
-      <c r="Y31" s="15"/>
-      <c r="Z31" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA31" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB31" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R31" s="7"/>
+      <c r="S31" s="13"/>
+      <c r="T31" s="14"/>
+      <c r="U31" s="15"/>
+      <c r="V31" s="16" t="str">
+        <f>IF(A31="","",IF(A31="결승","PO-FINAL",IF(B31="","번호 없음",IF(A31="PO","PO-"&amp;B31&amp;"M",A31&amp;"-"&amp;B31&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W31" s="16" t="str">
+        <f>IF(C31="","",IFERROR(CHOOSE(WEEKDAY(C31),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X31" s="16" t="str">
+        <f>IF(COUNTA(A31:R31)=0,"",IF(COUNTBLANK(A31:R31)-IF(A31="결승",IF(B31="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A31:R31)-IF(A31="결승",IF(B31="",1,0),0))&amp;"개",IF(D31=E31,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A32" s="7"/>
       <c r="B32" s="7"/>
       <c r="C32" s="11"/>
@@ -5616,28 +5469,24 @@
       <c r="O32" s="12"/>
       <c r="P32" s="7"/>
       <c r="Q32" s="7"/>
-      <c r="R32" s="12"/>
-      <c r="S32" s="12"/>
-      <c r="T32" s="7"/>
-      <c r="U32" s="7"/>
-      <c r="V32" s="7"/>
-      <c r="W32" s="13"/>
-      <c r="X32" s="14"/>
-      <c r="Y32" s="15"/>
-      <c r="Z32" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA32" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB32" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R32" s="7"/>
+      <c r="S32" s="13"/>
+      <c r="T32" s="14"/>
+      <c r="U32" s="15"/>
+      <c r="V32" s="16" t="str">
+        <f>IF(A32="","",IF(A32="결승","PO-FINAL",IF(B32="","번호 없음",IF(A32="PO","PO-"&amp;B32&amp;"M",A32&amp;"-"&amp;B32&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W32" s="16" t="str">
+        <f>IF(C32="","",IFERROR(CHOOSE(WEEKDAY(C32),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X32" s="16" t="str">
+        <f>IF(COUNTA(A32:R32)=0,"",IF(COUNTBLANK(A32:R32)-IF(A32="결승",IF(B32="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A32:R32)-IF(A32="결승",IF(B32="",1,0),0))&amp;"개",IF(D32=E32,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A33" s="7"/>
       <c r="B33" s="7"/>
       <c r="C33" s="11"/>
@@ -5655,28 +5504,24 @@
       <c r="O33" s="12"/>
       <c r="P33" s="7"/>
       <c r="Q33" s="7"/>
-      <c r="R33" s="12"/>
-      <c r="S33" s="12"/>
-      <c r="T33" s="7"/>
-      <c r="U33" s="7"/>
-      <c r="V33" s="7"/>
-      <c r="W33" s="13"/>
-      <c r="X33" s="14"/>
-      <c r="Y33" s="15"/>
-      <c r="Z33" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AA33" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="AB33" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R33" s="7"/>
+      <c r="S33" s="13"/>
+      <c r="T33" s="14"/>
+      <c r="U33" s="15"/>
+      <c r="V33" s="16" t="str">
+        <f>IF(A33="","",IF(A33="결승","PO-FINAL",IF(B33="","번호 없음",IF(A33="PO","PO-"&amp;B33&amp;"M",A33&amp;"-"&amp;B33&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W33" s="16" t="str">
+        <f>IF(C33="","",IFERROR(CHOOSE(WEEKDAY(C33),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X33" s="16" t="str">
+        <f>IF(COUNTA(A33:R33)=0,"",IF(COUNTBLANK(A33:R33)-IF(A33="결승",IF(B33="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A33:R33)-IF(A33="결승",IF(B33="",1,0),0))&amp;"개",IF(D33=E33,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="11"/>
@@ -5694,28 +5539,24 @@
       <c r="O34" s="12"/>
       <c r="P34" s="7"/>
       <c r="Q34" s="7"/>
-      <c r="R34" s="12"/>
-      <c r="S34" s="12"/>
-      <c r="T34" s="7"/>
-      <c r="U34" s="7"/>
-      <c r="V34" s="7"/>
-      <c r="W34" s="13"/>
-      <c r="X34" s="14"/>
-      <c r="Y34" s="15"/>
-      <c r="Z34" s="16" t="str">
-        <f t="shared" ref="Z34:Z65" si="3">IF(A34="","",IF(A34="결승","PO-FINAL",IF(B34="","번호 없음",IF(A34="PO","PO-"&amp;B34&amp;"M",A34&amp;"-"&amp;B34&amp;"M"))))</f>
-        <v/>
-      </c>
-      <c r="AA34" s="16" t="str">
-        <f t="shared" ref="AA34:AA65" si="4">IF(C34="","",IFERROR(CHOOSE(WEEKDAY(C34),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
-        <v/>
-      </c>
-      <c r="AB34" s="16" t="str">
-        <f t="shared" ref="AB34:AB65" si="5">IF(COUNTA(A34:V34)=0,"",IF(COUNTBLANK(A34:V34)-IF(A34="결승",IF(B34="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A34:V34)-IF(A34="결승",IF(B34="",1,0),0))&amp;"개",IF(D34=E34,"홈·원정 같음","OK")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R34" s="7"/>
+      <c r="S34" s="13"/>
+      <c r="T34" s="14"/>
+      <c r="U34" s="15"/>
+      <c r="V34" s="16" t="str">
+        <f>IF(A34="","",IF(A34="결승","PO-FINAL",IF(B34="","번호 없음",IF(A34="PO","PO-"&amp;B34&amp;"M",A34&amp;"-"&amp;B34&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W34" s="16" t="str">
+        <f>IF(C34="","",IFERROR(CHOOSE(WEEKDAY(C34),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X34" s="16" t="str">
+        <f>IF(COUNTA(A34:R34)=0,"",IF(COUNTBLANK(A34:R34)-IF(A34="결승",IF(B34="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A34:R34)-IF(A34="결승",IF(B34="",1,0),0))&amp;"개",IF(D34=E34,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A35" s="7"/>
       <c r="B35" s="7"/>
       <c r="C35" s="11"/>
@@ -5733,28 +5574,24 @@
       <c r="O35" s="12"/>
       <c r="P35" s="7"/>
       <c r="Q35" s="7"/>
-      <c r="R35" s="12"/>
-      <c r="S35" s="12"/>
-      <c r="T35" s="7"/>
-      <c r="U35" s="7"/>
-      <c r="V35" s="7"/>
-      <c r="W35" s="13"/>
-      <c r="X35" s="14"/>
-      <c r="Y35" s="15"/>
-      <c r="Z35" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AA35" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AB35" s="16" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R35" s="7"/>
+      <c r="S35" s="13"/>
+      <c r="T35" s="14"/>
+      <c r="U35" s="15"/>
+      <c r="V35" s="16" t="str">
+        <f>IF(A35="","",IF(A35="결승","PO-FINAL",IF(B35="","번호 없음",IF(A35="PO","PO-"&amp;B35&amp;"M",A35&amp;"-"&amp;B35&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W35" s="16" t="str">
+        <f>IF(C35="","",IFERROR(CHOOSE(WEEKDAY(C35),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X35" s="16" t="str">
+        <f>IF(COUNTA(A35:R35)=0,"",IF(COUNTBLANK(A35:R35)-IF(A35="결승",IF(B35="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A35:R35)-IF(A35="결승",IF(B35="",1,0),0))&amp;"개",IF(D35=E35,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
       <c r="C36" s="11"/>
@@ -5772,28 +5609,24 @@
       <c r="O36" s="12"/>
       <c r="P36" s="7"/>
       <c r="Q36" s="7"/>
-      <c r="R36" s="12"/>
-      <c r="S36" s="12"/>
-      <c r="T36" s="7"/>
-      <c r="U36" s="7"/>
-      <c r="V36" s="7"/>
-      <c r="W36" s="13"/>
-      <c r="X36" s="14"/>
-      <c r="Y36" s="15"/>
-      <c r="Z36" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AA36" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AB36" s="16" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R36" s="7"/>
+      <c r="S36" s="13"/>
+      <c r="T36" s="14"/>
+      <c r="U36" s="15"/>
+      <c r="V36" s="16" t="str">
+        <f>IF(A36="","",IF(A36="결승","PO-FINAL",IF(B36="","번호 없음",IF(A36="PO","PO-"&amp;B36&amp;"M",A36&amp;"-"&amp;B36&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W36" s="16" t="str">
+        <f>IF(C36="","",IFERROR(CHOOSE(WEEKDAY(C36),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X36" s="16" t="str">
+        <f>IF(COUNTA(A36:R36)=0,"",IF(COUNTBLANK(A36:R36)-IF(A36="결승",IF(B36="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A36:R36)-IF(A36="결승",IF(B36="",1,0),0))&amp;"개",IF(D36=E36,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
       <c r="C37" s="11"/>
@@ -5811,28 +5644,24 @@
       <c r="O37" s="12"/>
       <c r="P37" s="7"/>
       <c r="Q37" s="7"/>
-      <c r="R37" s="12"/>
-      <c r="S37" s="12"/>
-      <c r="T37" s="7"/>
-      <c r="U37" s="7"/>
-      <c r="V37" s="7"/>
-      <c r="W37" s="13"/>
-      <c r="X37" s="14"/>
-      <c r="Y37" s="15"/>
-      <c r="Z37" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AA37" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AB37" s="16" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R37" s="7"/>
+      <c r="S37" s="13"/>
+      <c r="T37" s="14"/>
+      <c r="U37" s="15"/>
+      <c r="V37" s="16" t="str">
+        <f>IF(A37="","",IF(A37="결승","PO-FINAL",IF(B37="","번호 없음",IF(A37="PO","PO-"&amp;B37&amp;"M",A37&amp;"-"&amp;B37&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W37" s="16" t="str">
+        <f>IF(C37="","",IFERROR(CHOOSE(WEEKDAY(C37),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X37" s="16" t="str">
+        <f>IF(COUNTA(A37:R37)=0,"",IF(COUNTBLANK(A37:R37)-IF(A37="결승",IF(B37="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A37:R37)-IF(A37="결승",IF(B37="",1,0),0))&amp;"개",IF(D37=E37,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
       <c r="C38" s="11"/>
@@ -5850,28 +5679,24 @@
       <c r="O38" s="12"/>
       <c r="P38" s="7"/>
       <c r="Q38" s="7"/>
-      <c r="R38" s="12"/>
-      <c r="S38" s="12"/>
-      <c r="T38" s="7"/>
-      <c r="U38" s="7"/>
-      <c r="V38" s="7"/>
-      <c r="W38" s="13"/>
-      <c r="X38" s="14"/>
-      <c r="Y38" s="15"/>
-      <c r="Z38" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AA38" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AB38" s="16" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R38" s="7"/>
+      <c r="S38" s="13"/>
+      <c r="T38" s="14"/>
+      <c r="U38" s="15"/>
+      <c r="V38" s="16" t="str">
+        <f>IF(A38="","",IF(A38="결승","PO-FINAL",IF(B38="","번호 없음",IF(A38="PO","PO-"&amp;B38&amp;"M",A38&amp;"-"&amp;B38&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W38" s="16" t="str">
+        <f>IF(C38="","",IFERROR(CHOOSE(WEEKDAY(C38),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X38" s="16" t="str">
+        <f>IF(COUNTA(A38:R38)=0,"",IF(COUNTBLANK(A38:R38)-IF(A38="결승",IF(B38="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A38:R38)-IF(A38="결승",IF(B38="",1,0),0))&amp;"개",IF(D38=E38,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A39" s="7"/>
       <c r="B39" s="7"/>
       <c r="C39" s="11"/>
@@ -5889,28 +5714,24 @@
       <c r="O39" s="12"/>
       <c r="P39" s="7"/>
       <c r="Q39" s="7"/>
-      <c r="R39" s="12"/>
-      <c r="S39" s="12"/>
-      <c r="T39" s="7"/>
-      <c r="U39" s="7"/>
-      <c r="V39" s="7"/>
-      <c r="W39" s="13"/>
-      <c r="X39" s="14"/>
-      <c r="Y39" s="15"/>
-      <c r="Z39" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AA39" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AB39" s="16" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R39" s="7"/>
+      <c r="S39" s="13"/>
+      <c r="T39" s="14"/>
+      <c r="U39" s="15"/>
+      <c r="V39" s="16" t="str">
+        <f>IF(A39="","",IF(A39="결승","PO-FINAL",IF(B39="","번호 없음",IF(A39="PO","PO-"&amp;B39&amp;"M",A39&amp;"-"&amp;B39&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W39" s="16" t="str">
+        <f>IF(C39="","",IFERROR(CHOOSE(WEEKDAY(C39),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X39" s="16" t="str">
+        <f>IF(COUNTA(A39:R39)=0,"",IF(COUNTBLANK(A39:R39)-IF(A39="결승",IF(B39="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A39:R39)-IF(A39="결승",IF(B39="",1,0),0))&amp;"개",IF(D39=E39,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="11"/>
@@ -5928,28 +5749,24 @@
       <c r="O40" s="12"/>
       <c r="P40" s="7"/>
       <c r="Q40" s="7"/>
-      <c r="R40" s="12"/>
-      <c r="S40" s="12"/>
-      <c r="T40" s="7"/>
-      <c r="U40" s="7"/>
-      <c r="V40" s="7"/>
-      <c r="W40" s="13"/>
-      <c r="X40" s="14"/>
-      <c r="Y40" s="15"/>
-      <c r="Z40" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AA40" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AB40" s="16" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R40" s="7"/>
+      <c r="S40" s="13"/>
+      <c r="T40" s="14"/>
+      <c r="U40" s="15"/>
+      <c r="V40" s="16" t="str">
+        <f>IF(A40="","",IF(A40="결승","PO-FINAL",IF(B40="","번호 없음",IF(A40="PO","PO-"&amp;B40&amp;"M",A40&amp;"-"&amp;B40&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W40" s="16" t="str">
+        <f>IF(C40="","",IFERROR(CHOOSE(WEEKDAY(C40),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X40" s="16" t="str">
+        <f>IF(COUNTA(A40:R40)=0,"",IF(COUNTBLANK(A40:R40)-IF(A40="결승",IF(B40="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A40:R40)-IF(A40="결승",IF(B40="",1,0),0))&amp;"개",IF(D40=E40,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A41" s="7"/>
       <c r="B41" s="7"/>
       <c r="C41" s="11"/>
@@ -5967,28 +5784,24 @@
       <c r="O41" s="12"/>
       <c r="P41" s="7"/>
       <c r="Q41" s="7"/>
-      <c r="R41" s="12"/>
-      <c r="S41" s="12"/>
-      <c r="T41" s="7"/>
-      <c r="U41" s="7"/>
-      <c r="V41" s="7"/>
-      <c r="W41" s="13"/>
-      <c r="X41" s="14"/>
-      <c r="Y41" s="15"/>
-      <c r="Z41" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AA41" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AB41" s="16" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R41" s="7"/>
+      <c r="S41" s="13"/>
+      <c r="T41" s="14"/>
+      <c r="U41" s="15"/>
+      <c r="V41" s="16" t="str">
+        <f>IF(A41="","",IF(A41="결승","PO-FINAL",IF(B41="","번호 없음",IF(A41="PO","PO-"&amp;B41&amp;"M",A41&amp;"-"&amp;B41&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W41" s="16" t="str">
+        <f>IF(C41="","",IFERROR(CHOOSE(WEEKDAY(C41),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X41" s="16" t="str">
+        <f>IF(COUNTA(A41:R41)=0,"",IF(COUNTBLANK(A41:R41)-IF(A41="결승",IF(B41="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A41:R41)-IF(A41="결승",IF(B41="",1,0),0))&amp;"개",IF(D41=E41,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A42" s="7"/>
       <c r="B42" s="7"/>
       <c r="C42" s="11"/>
@@ -6006,28 +5819,24 @@
       <c r="O42" s="12"/>
       <c r="P42" s="7"/>
       <c r="Q42" s="7"/>
-      <c r="R42" s="12"/>
-      <c r="S42" s="12"/>
-      <c r="T42" s="7"/>
-      <c r="U42" s="7"/>
-      <c r="V42" s="7"/>
-      <c r="W42" s="13"/>
-      <c r="X42" s="14"/>
-      <c r="Y42" s="15"/>
-      <c r="Z42" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AA42" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AB42" s="16" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="43" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R42" s="7"/>
+      <c r="S42" s="13"/>
+      <c r="T42" s="14"/>
+      <c r="U42" s="15"/>
+      <c r="V42" s="16" t="str">
+        <f>IF(A42="","",IF(A42="결승","PO-FINAL",IF(B42="","번호 없음",IF(A42="PO","PO-"&amp;B42&amp;"M",A42&amp;"-"&amp;B42&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W42" s="16" t="str">
+        <f>IF(C42="","",IFERROR(CHOOSE(WEEKDAY(C42),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X42" s="16" t="str">
+        <f>IF(COUNTA(A42:R42)=0,"",IF(COUNTBLANK(A42:R42)-IF(A42="결승",IF(B42="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A42:R42)-IF(A42="결승",IF(B42="",1,0),0))&amp;"개",IF(D42=E42,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A43" s="7"/>
       <c r="B43" s="7"/>
       <c r="C43" s="11"/>
@@ -6045,28 +5854,24 @@
       <c r="O43" s="12"/>
       <c r="P43" s="7"/>
       <c r="Q43" s="7"/>
-      <c r="R43" s="12"/>
-      <c r="S43" s="12"/>
-      <c r="T43" s="7"/>
-      <c r="U43" s="7"/>
-      <c r="V43" s="7"/>
-      <c r="W43" s="13"/>
-      <c r="X43" s="14"/>
-      <c r="Y43" s="15"/>
-      <c r="Z43" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AA43" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AB43" s="16" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="44" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R43" s="7"/>
+      <c r="S43" s="13"/>
+      <c r="T43" s="14"/>
+      <c r="U43" s="15"/>
+      <c r="V43" s="16" t="str">
+        <f>IF(A43="","",IF(A43="결승","PO-FINAL",IF(B43="","번호 없음",IF(A43="PO","PO-"&amp;B43&amp;"M",A43&amp;"-"&amp;B43&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W43" s="16" t="str">
+        <f>IF(C43="","",IFERROR(CHOOSE(WEEKDAY(C43),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X43" s="16" t="str">
+        <f>IF(COUNTA(A43:R43)=0,"",IF(COUNTBLANK(A43:R43)-IF(A43="결승",IF(B43="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A43:R43)-IF(A43="결승",IF(B43="",1,0),0))&amp;"개",IF(D43=E43,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A44" s="7"/>
       <c r="B44" s="7"/>
       <c r="C44" s="11"/>
@@ -6084,28 +5889,24 @@
       <c r="O44" s="12"/>
       <c r="P44" s="7"/>
       <c r="Q44" s="7"/>
-      <c r="R44" s="12"/>
-      <c r="S44" s="12"/>
-      <c r="T44" s="7"/>
-      <c r="U44" s="7"/>
-      <c r="V44" s="7"/>
-      <c r="W44" s="13"/>
-      <c r="X44" s="14"/>
-      <c r="Y44" s="15"/>
-      <c r="Z44" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AA44" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AB44" s="16" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="45" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R44" s="7"/>
+      <c r="S44" s="13"/>
+      <c r="T44" s="14"/>
+      <c r="U44" s="15"/>
+      <c r="V44" s="16" t="str">
+        <f>IF(A44="","",IF(A44="결승","PO-FINAL",IF(B44="","번호 없음",IF(A44="PO","PO-"&amp;B44&amp;"M",A44&amp;"-"&amp;B44&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W44" s="16" t="str">
+        <f>IF(C44="","",IFERROR(CHOOSE(WEEKDAY(C44),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X44" s="16" t="str">
+        <f>IF(COUNTA(A44:R44)=0,"",IF(COUNTBLANK(A44:R44)-IF(A44="결승",IF(B44="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A44:R44)-IF(A44="결승",IF(B44="",1,0),0))&amp;"개",IF(D44=E44,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A45" s="7"/>
       <c r="B45" s="7"/>
       <c r="C45" s="11"/>
@@ -6123,28 +5924,24 @@
       <c r="O45" s="12"/>
       <c r="P45" s="7"/>
       <c r="Q45" s="7"/>
-      <c r="R45" s="12"/>
-      <c r="S45" s="12"/>
-      <c r="T45" s="7"/>
-      <c r="U45" s="7"/>
-      <c r="V45" s="7"/>
-      <c r="W45" s="13"/>
-      <c r="X45" s="14"/>
-      <c r="Y45" s="15"/>
-      <c r="Z45" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AA45" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AB45" s="16" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="46" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R45" s="7"/>
+      <c r="S45" s="13"/>
+      <c r="T45" s="14"/>
+      <c r="U45" s="15"/>
+      <c r="V45" s="16" t="str">
+        <f>IF(A45="","",IF(A45="결승","PO-FINAL",IF(B45="","번호 없음",IF(A45="PO","PO-"&amp;B45&amp;"M",A45&amp;"-"&amp;B45&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W45" s="16" t="str">
+        <f>IF(C45="","",IFERROR(CHOOSE(WEEKDAY(C45),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X45" s="16" t="str">
+        <f>IF(COUNTA(A45:R45)=0,"",IF(COUNTBLANK(A45:R45)-IF(A45="결승",IF(B45="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A45:R45)-IF(A45="결승",IF(B45="",1,0),0))&amp;"개",IF(D45=E45,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A46" s="7"/>
       <c r="B46" s="7"/>
       <c r="C46" s="11"/>
@@ -6162,28 +5959,24 @@
       <c r="O46" s="12"/>
       <c r="P46" s="7"/>
       <c r="Q46" s="7"/>
-      <c r="R46" s="12"/>
-      <c r="S46" s="12"/>
-      <c r="T46" s="7"/>
-      <c r="U46" s="7"/>
-      <c r="V46" s="7"/>
-      <c r="W46" s="13"/>
-      <c r="X46" s="14"/>
-      <c r="Y46" s="15"/>
-      <c r="Z46" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AA46" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AB46" s="16" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="47" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R46" s="7"/>
+      <c r="S46" s="13"/>
+      <c r="T46" s="14"/>
+      <c r="U46" s="15"/>
+      <c r="V46" s="16" t="str">
+        <f>IF(A46="","",IF(A46="결승","PO-FINAL",IF(B46="","번호 없음",IF(A46="PO","PO-"&amp;B46&amp;"M",A46&amp;"-"&amp;B46&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W46" s="16" t="str">
+        <f>IF(C46="","",IFERROR(CHOOSE(WEEKDAY(C46),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X46" s="16" t="str">
+        <f>IF(COUNTA(A46:R46)=0,"",IF(COUNTBLANK(A46:R46)-IF(A46="결승",IF(B46="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A46:R46)-IF(A46="결승",IF(B46="",1,0),0))&amp;"개",IF(D46=E46,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A47" s="7"/>
       <c r="B47" s="7"/>
       <c r="C47" s="11"/>
@@ -6201,28 +5994,24 @@
       <c r="O47" s="12"/>
       <c r="P47" s="7"/>
       <c r="Q47" s="7"/>
-      <c r="R47" s="12"/>
-      <c r="S47" s="12"/>
-      <c r="T47" s="7"/>
-      <c r="U47" s="7"/>
-      <c r="V47" s="7"/>
-      <c r="W47" s="13"/>
-      <c r="X47" s="14"/>
-      <c r="Y47" s="15"/>
-      <c r="Z47" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AA47" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AB47" s="16" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="48" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R47" s="7"/>
+      <c r="S47" s="13"/>
+      <c r="T47" s="14"/>
+      <c r="U47" s="15"/>
+      <c r="V47" s="16" t="str">
+        <f>IF(A47="","",IF(A47="결승","PO-FINAL",IF(B47="","번호 없음",IF(A47="PO","PO-"&amp;B47&amp;"M",A47&amp;"-"&amp;B47&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W47" s="16" t="str">
+        <f>IF(C47="","",IFERROR(CHOOSE(WEEKDAY(C47),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X47" s="16" t="str">
+        <f>IF(COUNTA(A47:R47)=0,"",IF(COUNTBLANK(A47:R47)-IF(A47="결승",IF(B47="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A47:R47)-IF(A47="결승",IF(B47="",1,0),0))&amp;"개",IF(D47=E47,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A48" s="7"/>
       <c r="B48" s="7"/>
       <c r="C48" s="11"/>
@@ -6240,28 +6029,24 @@
       <c r="O48" s="12"/>
       <c r="P48" s="7"/>
       <c r="Q48" s="7"/>
-      <c r="R48" s="12"/>
-      <c r="S48" s="12"/>
-      <c r="T48" s="7"/>
-      <c r="U48" s="7"/>
-      <c r="V48" s="7"/>
-      <c r="W48" s="13"/>
-      <c r="X48" s="14"/>
-      <c r="Y48" s="15"/>
-      <c r="Z48" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AA48" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AB48" s="16" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="49" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R48" s="7"/>
+      <c r="S48" s="13"/>
+      <c r="T48" s="14"/>
+      <c r="U48" s="15"/>
+      <c r="V48" s="16" t="str">
+        <f>IF(A48="","",IF(A48="결승","PO-FINAL",IF(B48="","번호 없음",IF(A48="PO","PO-"&amp;B48&amp;"M",A48&amp;"-"&amp;B48&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W48" s="16" t="str">
+        <f>IF(C48="","",IFERROR(CHOOSE(WEEKDAY(C48),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X48" s="16" t="str">
+        <f>IF(COUNTA(A48:R48)=0,"",IF(COUNTBLANK(A48:R48)-IF(A48="결승",IF(B48="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A48:R48)-IF(A48="결승",IF(B48="",1,0),0))&amp;"개",IF(D48=E48,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A49" s="7"/>
       <c r="B49" s="7"/>
       <c r="C49" s="11"/>
@@ -6279,28 +6064,24 @@
       <c r="O49" s="12"/>
       <c r="P49" s="7"/>
       <c r="Q49" s="7"/>
-      <c r="R49" s="12"/>
-      <c r="S49" s="12"/>
-      <c r="T49" s="7"/>
-      <c r="U49" s="7"/>
-      <c r="V49" s="7"/>
-      <c r="W49" s="13"/>
-      <c r="X49" s="14"/>
-      <c r="Y49" s="15"/>
-      <c r="Z49" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AA49" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AB49" s="16" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="50" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R49" s="7"/>
+      <c r="S49" s="13"/>
+      <c r="T49" s="14"/>
+      <c r="U49" s="15"/>
+      <c r="V49" s="16" t="str">
+        <f>IF(A49="","",IF(A49="결승","PO-FINAL",IF(B49="","번호 없음",IF(A49="PO","PO-"&amp;B49&amp;"M",A49&amp;"-"&amp;B49&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W49" s="16" t="str">
+        <f>IF(C49="","",IFERROR(CHOOSE(WEEKDAY(C49),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X49" s="16" t="str">
+        <f>IF(COUNTA(A49:R49)=0,"",IF(COUNTBLANK(A49:R49)-IF(A49="결승",IF(B49="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A49:R49)-IF(A49="결승",IF(B49="",1,0),0))&amp;"개",IF(D49=E49,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="11"/>
@@ -6318,28 +6099,24 @@
       <c r="O50" s="12"/>
       <c r="P50" s="7"/>
       <c r="Q50" s="7"/>
-      <c r="R50" s="12"/>
-      <c r="S50" s="12"/>
-      <c r="T50" s="7"/>
-      <c r="U50" s="7"/>
-      <c r="V50" s="7"/>
-      <c r="W50" s="13"/>
-      <c r="X50" s="14"/>
-      <c r="Y50" s="15"/>
-      <c r="Z50" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AA50" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AB50" s="16" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="51" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R50" s="7"/>
+      <c r="S50" s="13"/>
+      <c r="T50" s="14"/>
+      <c r="U50" s="15"/>
+      <c r="V50" s="16" t="str">
+        <f>IF(A50="","",IF(A50="결승","PO-FINAL",IF(B50="","번호 없음",IF(A50="PO","PO-"&amp;B50&amp;"M",A50&amp;"-"&amp;B50&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W50" s="16" t="str">
+        <f>IF(C50="","",IFERROR(CHOOSE(WEEKDAY(C50),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X50" s="16" t="str">
+        <f>IF(COUNTA(A50:R50)=0,"",IF(COUNTBLANK(A50:R50)-IF(A50="결승",IF(B50="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A50:R50)-IF(A50="결승",IF(B50="",1,0),0))&amp;"개",IF(D50=E50,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A51" s="7"/>
       <c r="B51" s="7"/>
       <c r="C51" s="11"/>
@@ -6357,28 +6134,24 @@
       <c r="O51" s="12"/>
       <c r="P51" s="7"/>
       <c r="Q51" s="7"/>
-      <c r="R51" s="12"/>
-      <c r="S51" s="12"/>
-      <c r="T51" s="7"/>
-      <c r="U51" s="7"/>
-      <c r="V51" s="7"/>
-      <c r="W51" s="13"/>
-      <c r="X51" s="14"/>
-      <c r="Y51" s="15"/>
-      <c r="Z51" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AA51" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AB51" s="16" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="52" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R51" s="7"/>
+      <c r="S51" s="13"/>
+      <c r="T51" s="14"/>
+      <c r="U51" s="15"/>
+      <c r="V51" s="16" t="str">
+        <f>IF(A51="","",IF(A51="결승","PO-FINAL",IF(B51="","번호 없음",IF(A51="PO","PO-"&amp;B51&amp;"M",A51&amp;"-"&amp;B51&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W51" s="16" t="str">
+        <f>IF(C51="","",IFERROR(CHOOSE(WEEKDAY(C51),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X51" s="16" t="str">
+        <f>IF(COUNTA(A51:R51)=0,"",IF(COUNTBLANK(A51:R51)-IF(A51="결승",IF(B51="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A51:R51)-IF(A51="결승",IF(B51="",1,0),0))&amp;"개",IF(D51=E51,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A52" s="7"/>
       <c r="B52" s="7"/>
       <c r="C52" s="11"/>
@@ -6396,28 +6169,24 @@
       <c r="O52" s="12"/>
       <c r="P52" s="7"/>
       <c r="Q52" s="7"/>
-      <c r="R52" s="12"/>
-      <c r="S52" s="12"/>
-      <c r="T52" s="7"/>
-      <c r="U52" s="7"/>
-      <c r="V52" s="7"/>
-      <c r="W52" s="13"/>
-      <c r="X52" s="14"/>
-      <c r="Y52" s="15"/>
-      <c r="Z52" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AA52" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AB52" s="16" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="53" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R52" s="7"/>
+      <c r="S52" s="13"/>
+      <c r="T52" s="14"/>
+      <c r="U52" s="15"/>
+      <c r="V52" s="16" t="str">
+        <f>IF(A52="","",IF(A52="결승","PO-FINAL",IF(B52="","번호 없음",IF(A52="PO","PO-"&amp;B52&amp;"M",A52&amp;"-"&amp;B52&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W52" s="16" t="str">
+        <f>IF(C52="","",IFERROR(CHOOSE(WEEKDAY(C52),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X52" s="16" t="str">
+        <f>IF(COUNTA(A52:R52)=0,"",IF(COUNTBLANK(A52:R52)-IF(A52="결승",IF(B52="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A52:R52)-IF(A52="결승",IF(B52="",1,0),0))&amp;"개",IF(D52=E52,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A53" s="7"/>
       <c r="B53" s="7"/>
       <c r="C53" s="11"/>
@@ -6435,28 +6204,24 @@
       <c r="O53" s="12"/>
       <c r="P53" s="7"/>
       <c r="Q53" s="7"/>
-      <c r="R53" s="12"/>
-      <c r="S53" s="12"/>
-      <c r="T53" s="7"/>
-      <c r="U53" s="7"/>
-      <c r="V53" s="7"/>
-      <c r="W53" s="13"/>
-      <c r="X53" s="14"/>
-      <c r="Y53" s="15"/>
-      <c r="Z53" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AA53" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AB53" s="16" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="54" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R53" s="7"/>
+      <c r="S53" s="13"/>
+      <c r="T53" s="14"/>
+      <c r="U53" s="15"/>
+      <c r="V53" s="16" t="str">
+        <f>IF(A53="","",IF(A53="결승","PO-FINAL",IF(B53="","번호 없음",IF(A53="PO","PO-"&amp;B53&amp;"M",A53&amp;"-"&amp;B53&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W53" s="16" t="str">
+        <f>IF(C53="","",IFERROR(CHOOSE(WEEKDAY(C53),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X53" s="16" t="str">
+        <f>IF(COUNTA(A53:R53)=0,"",IF(COUNTBLANK(A53:R53)-IF(A53="결승",IF(B53="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A53:R53)-IF(A53="결승",IF(B53="",1,0),0))&amp;"개",IF(D53=E53,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A54" s="7"/>
       <c r="B54" s="7"/>
       <c r="C54" s="11"/>
@@ -6474,28 +6239,24 @@
       <c r="O54" s="12"/>
       <c r="P54" s="7"/>
       <c r="Q54" s="7"/>
-      <c r="R54" s="12"/>
-      <c r="S54" s="12"/>
-      <c r="T54" s="7"/>
-      <c r="U54" s="7"/>
-      <c r="V54" s="7"/>
-      <c r="W54" s="13"/>
-      <c r="X54" s="14"/>
-      <c r="Y54" s="15"/>
-      <c r="Z54" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AA54" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AB54" s="16" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="55" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R54" s="7"/>
+      <c r="S54" s="13"/>
+      <c r="T54" s="14"/>
+      <c r="U54" s="15"/>
+      <c r="V54" s="16" t="str">
+        <f>IF(A54="","",IF(A54="결승","PO-FINAL",IF(B54="","번호 없음",IF(A54="PO","PO-"&amp;B54&amp;"M",A54&amp;"-"&amp;B54&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W54" s="16" t="str">
+        <f>IF(C54="","",IFERROR(CHOOSE(WEEKDAY(C54),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X54" s="16" t="str">
+        <f>IF(COUNTA(A54:R54)=0,"",IF(COUNTBLANK(A54:R54)-IF(A54="결승",IF(B54="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A54:R54)-IF(A54="결승",IF(B54="",1,0),0))&amp;"개",IF(D54=E54,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A55" s="7"/>
       <c r="B55" s="7"/>
       <c r="C55" s="11"/>
@@ -6513,28 +6274,24 @@
       <c r="O55" s="12"/>
       <c r="P55" s="7"/>
       <c r="Q55" s="7"/>
-      <c r="R55" s="12"/>
-      <c r="S55" s="12"/>
-      <c r="T55" s="7"/>
-      <c r="U55" s="7"/>
-      <c r="V55" s="7"/>
-      <c r="W55" s="13"/>
-      <c r="X55" s="14"/>
-      <c r="Y55" s="15"/>
-      <c r="Z55" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AA55" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AB55" s="16" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="56" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R55" s="7"/>
+      <c r="S55" s="13"/>
+      <c r="T55" s="14"/>
+      <c r="U55" s="15"/>
+      <c r="V55" s="16" t="str">
+        <f>IF(A55="","",IF(A55="결승","PO-FINAL",IF(B55="","번호 없음",IF(A55="PO","PO-"&amp;B55&amp;"M",A55&amp;"-"&amp;B55&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W55" s="16" t="str">
+        <f>IF(C55="","",IFERROR(CHOOSE(WEEKDAY(C55),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X55" s="16" t="str">
+        <f>IF(COUNTA(A55:R55)=0,"",IF(COUNTBLANK(A55:R55)-IF(A55="결승",IF(B55="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A55:R55)-IF(A55="결승",IF(B55="",1,0),0))&amp;"개",IF(D55=E55,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A56" s="7"/>
       <c r="B56" s="7"/>
       <c r="C56" s="11"/>
@@ -6552,28 +6309,24 @@
       <c r="O56" s="12"/>
       <c r="P56" s="7"/>
       <c r="Q56" s="7"/>
-      <c r="R56" s="12"/>
-      <c r="S56" s="12"/>
-      <c r="T56" s="7"/>
-      <c r="U56" s="7"/>
-      <c r="V56" s="7"/>
-      <c r="W56" s="13"/>
-      <c r="X56" s="14"/>
-      <c r="Y56" s="15"/>
-      <c r="Z56" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AA56" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AB56" s="16" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="57" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R56" s="7"/>
+      <c r="S56" s="13"/>
+      <c r="T56" s="14"/>
+      <c r="U56" s="15"/>
+      <c r="V56" s="16" t="str">
+        <f>IF(A56="","",IF(A56="결승","PO-FINAL",IF(B56="","번호 없음",IF(A56="PO","PO-"&amp;B56&amp;"M",A56&amp;"-"&amp;B56&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W56" s="16" t="str">
+        <f>IF(C56="","",IFERROR(CHOOSE(WEEKDAY(C56),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X56" s="16" t="str">
+        <f>IF(COUNTA(A56:R56)=0,"",IF(COUNTBLANK(A56:R56)-IF(A56="결승",IF(B56="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A56:R56)-IF(A56="결승",IF(B56="",1,0),0))&amp;"개",IF(D56=E56,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A57" s="7"/>
       <c r="B57" s="7"/>
       <c r="C57" s="11"/>
@@ -6591,28 +6344,24 @@
       <c r="O57" s="12"/>
       <c r="P57" s="7"/>
       <c r="Q57" s="7"/>
-      <c r="R57" s="12"/>
-      <c r="S57" s="12"/>
-      <c r="T57" s="7"/>
-      <c r="U57" s="7"/>
-      <c r="V57" s="7"/>
-      <c r="W57" s="13"/>
-      <c r="X57" s="14"/>
-      <c r="Y57" s="15"/>
-      <c r="Z57" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AA57" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AB57" s="16" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="58" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R57" s="7"/>
+      <c r="S57" s="13"/>
+      <c r="T57" s="14"/>
+      <c r="U57" s="15"/>
+      <c r="V57" s="16" t="str">
+        <f>IF(A57="","",IF(A57="결승","PO-FINAL",IF(B57="","번호 없음",IF(A57="PO","PO-"&amp;B57&amp;"M",A57&amp;"-"&amp;B57&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W57" s="16" t="str">
+        <f>IF(C57="","",IFERROR(CHOOSE(WEEKDAY(C57),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X57" s="16" t="str">
+        <f>IF(COUNTA(A57:R57)=0,"",IF(COUNTBLANK(A57:R57)-IF(A57="결승",IF(B57="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A57:R57)-IF(A57="결승",IF(B57="",1,0),0))&amp;"개",IF(D57=E57,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A58" s="7"/>
       <c r="B58" s="7"/>
       <c r="C58" s="11"/>
@@ -6630,28 +6379,24 @@
       <c r="O58" s="12"/>
       <c r="P58" s="7"/>
       <c r="Q58" s="7"/>
-      <c r="R58" s="12"/>
-      <c r="S58" s="12"/>
-      <c r="T58" s="7"/>
-      <c r="U58" s="7"/>
-      <c r="V58" s="7"/>
-      <c r="W58" s="13"/>
-      <c r="X58" s="14"/>
-      <c r="Y58" s="15"/>
-      <c r="Z58" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AA58" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AB58" s="16" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="59" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R58" s="7"/>
+      <c r="S58" s="13"/>
+      <c r="T58" s="14"/>
+      <c r="U58" s="15"/>
+      <c r="V58" s="16" t="str">
+        <f>IF(A58="","",IF(A58="결승","PO-FINAL",IF(B58="","번호 없음",IF(A58="PO","PO-"&amp;B58&amp;"M",A58&amp;"-"&amp;B58&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W58" s="16" t="str">
+        <f>IF(C58="","",IFERROR(CHOOSE(WEEKDAY(C58),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X58" s="16" t="str">
+        <f>IF(COUNTA(A58:R58)=0,"",IF(COUNTBLANK(A58:R58)-IF(A58="결승",IF(B58="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A58:R58)-IF(A58="결승",IF(B58="",1,0),0))&amp;"개",IF(D58=E58,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A59" s="7"/>
       <c r="B59" s="7"/>
       <c r="C59" s="11"/>
@@ -6669,28 +6414,24 @@
       <c r="O59" s="12"/>
       <c r="P59" s="7"/>
       <c r="Q59" s="7"/>
-      <c r="R59" s="12"/>
-      <c r="S59" s="12"/>
-      <c r="T59" s="7"/>
-      <c r="U59" s="7"/>
-      <c r="V59" s="7"/>
-      <c r="W59" s="13"/>
-      <c r="X59" s="14"/>
-      <c r="Y59" s="15"/>
-      <c r="Z59" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AA59" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AB59" s="16" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="60" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R59" s="7"/>
+      <c r="S59" s="13"/>
+      <c r="T59" s="14"/>
+      <c r="U59" s="15"/>
+      <c r="V59" s="16" t="str">
+        <f>IF(A59="","",IF(A59="결승","PO-FINAL",IF(B59="","번호 없음",IF(A59="PO","PO-"&amp;B59&amp;"M",A59&amp;"-"&amp;B59&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W59" s="16" t="str">
+        <f>IF(C59="","",IFERROR(CHOOSE(WEEKDAY(C59),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X59" s="16" t="str">
+        <f>IF(COUNTA(A59:R59)=0,"",IF(COUNTBLANK(A59:R59)-IF(A59="결승",IF(B59="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A59:R59)-IF(A59="결승",IF(B59="",1,0),0))&amp;"개",IF(D59=E59,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="11"/>
@@ -6708,28 +6449,24 @@
       <c r="O60" s="12"/>
       <c r="P60" s="7"/>
       <c r="Q60" s="7"/>
-      <c r="R60" s="12"/>
-      <c r="S60" s="12"/>
-      <c r="T60" s="7"/>
-      <c r="U60" s="7"/>
-      <c r="V60" s="7"/>
-      <c r="W60" s="13"/>
-      <c r="X60" s="14"/>
-      <c r="Y60" s="15"/>
-      <c r="Z60" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AA60" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AB60" s="16" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="61" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R60" s="7"/>
+      <c r="S60" s="13"/>
+      <c r="T60" s="14"/>
+      <c r="U60" s="15"/>
+      <c r="V60" s="16" t="str">
+        <f>IF(A60="","",IF(A60="결승","PO-FINAL",IF(B60="","번호 없음",IF(A60="PO","PO-"&amp;B60&amp;"M",A60&amp;"-"&amp;B60&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W60" s="16" t="str">
+        <f>IF(C60="","",IFERROR(CHOOSE(WEEKDAY(C60),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X60" s="16" t="str">
+        <f>IF(COUNTA(A60:R60)=0,"",IF(COUNTBLANK(A60:R60)-IF(A60="결승",IF(B60="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A60:R60)-IF(A60="결승",IF(B60="",1,0),0))&amp;"개",IF(D60=E60,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A61" s="7"/>
       <c r="B61" s="7"/>
       <c r="C61" s="11"/>
@@ -6747,28 +6484,24 @@
       <c r="O61" s="12"/>
       <c r="P61" s="7"/>
       <c r="Q61" s="7"/>
-      <c r="R61" s="12"/>
-      <c r="S61" s="12"/>
-      <c r="T61" s="7"/>
-      <c r="U61" s="7"/>
-      <c r="V61" s="7"/>
-      <c r="W61" s="13"/>
-      <c r="X61" s="14"/>
-      <c r="Y61" s="15"/>
-      <c r="Z61" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AA61" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AB61" s="16" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="62" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R61" s="7"/>
+      <c r="S61" s="13"/>
+      <c r="T61" s="14"/>
+      <c r="U61" s="15"/>
+      <c r="V61" s="16" t="str">
+        <f>IF(A61="","",IF(A61="결승","PO-FINAL",IF(B61="","번호 없음",IF(A61="PO","PO-"&amp;B61&amp;"M",A61&amp;"-"&amp;B61&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W61" s="16" t="str">
+        <f>IF(C61="","",IFERROR(CHOOSE(WEEKDAY(C61),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X61" s="16" t="str">
+        <f>IF(COUNTA(A61:R61)=0,"",IF(COUNTBLANK(A61:R61)-IF(A61="결승",IF(B61="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A61:R61)-IF(A61="결승",IF(B61="",1,0),0))&amp;"개",IF(D61=E61,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A62" s="7"/>
       <c r="B62" s="7"/>
       <c r="C62" s="11"/>
@@ -6786,28 +6519,24 @@
       <c r="O62" s="12"/>
       <c r="P62" s="7"/>
       <c r="Q62" s="7"/>
-      <c r="R62" s="12"/>
-      <c r="S62" s="12"/>
-      <c r="T62" s="7"/>
-      <c r="U62" s="7"/>
-      <c r="V62" s="7"/>
-      <c r="W62" s="13"/>
-      <c r="X62" s="14"/>
-      <c r="Y62" s="15"/>
-      <c r="Z62" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AA62" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AB62" s="16" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="63" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R62" s="7"/>
+      <c r="S62" s="13"/>
+      <c r="T62" s="14"/>
+      <c r="U62" s="15"/>
+      <c r="V62" s="16" t="str">
+        <f>IF(A62="","",IF(A62="결승","PO-FINAL",IF(B62="","번호 없음",IF(A62="PO","PO-"&amp;B62&amp;"M",A62&amp;"-"&amp;B62&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W62" s="16" t="str">
+        <f>IF(C62="","",IFERROR(CHOOSE(WEEKDAY(C62),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X62" s="16" t="str">
+        <f>IF(COUNTA(A62:R62)=0,"",IF(COUNTBLANK(A62:R62)-IF(A62="결승",IF(B62="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A62:R62)-IF(A62="결승",IF(B62="",1,0),0))&amp;"개",IF(D62=E62,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A63" s="7"/>
       <c r="B63" s="7"/>
       <c r="C63" s="11"/>
@@ -6825,28 +6554,24 @@
       <c r="O63" s="12"/>
       <c r="P63" s="7"/>
       <c r="Q63" s="7"/>
-      <c r="R63" s="12"/>
-      <c r="S63" s="12"/>
-      <c r="T63" s="7"/>
-      <c r="U63" s="7"/>
-      <c r="V63" s="7"/>
-      <c r="W63" s="13"/>
-      <c r="X63" s="14"/>
-      <c r="Y63" s="15"/>
-      <c r="Z63" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AA63" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AB63" s="16" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="64" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R63" s="7"/>
+      <c r="S63" s="13"/>
+      <c r="T63" s="14"/>
+      <c r="U63" s="15"/>
+      <c r="V63" s="16" t="str">
+        <f>IF(A63="","",IF(A63="결승","PO-FINAL",IF(B63="","번호 없음",IF(A63="PO","PO-"&amp;B63&amp;"M",A63&amp;"-"&amp;B63&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W63" s="16" t="str">
+        <f>IF(C63="","",IFERROR(CHOOSE(WEEKDAY(C63),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X63" s="16" t="str">
+        <f>IF(COUNTA(A63:R63)=0,"",IF(COUNTBLANK(A63:R63)-IF(A63="결승",IF(B63="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A63:R63)-IF(A63="결승",IF(B63="",1,0),0))&amp;"개",IF(D63=E63,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A64" s="7"/>
       <c r="B64" s="7"/>
       <c r="C64" s="11"/>
@@ -6864,28 +6589,24 @@
       <c r="O64" s="12"/>
       <c r="P64" s="7"/>
       <c r="Q64" s="7"/>
-      <c r="R64" s="12"/>
-      <c r="S64" s="12"/>
-      <c r="T64" s="7"/>
-      <c r="U64" s="7"/>
-      <c r="V64" s="7"/>
-      <c r="W64" s="13"/>
-      <c r="X64" s="14"/>
-      <c r="Y64" s="15"/>
-      <c r="Z64" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AA64" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AB64" s="16" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="65" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R64" s="7"/>
+      <c r="S64" s="13"/>
+      <c r="T64" s="14"/>
+      <c r="U64" s="15"/>
+      <c r="V64" s="16" t="str">
+        <f>IF(A64="","",IF(A64="결승","PO-FINAL",IF(B64="","번호 없음",IF(A64="PO","PO-"&amp;B64&amp;"M",A64&amp;"-"&amp;B64&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W64" s="16" t="str">
+        <f>IF(C64="","",IFERROR(CHOOSE(WEEKDAY(C64),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X64" s="16" t="str">
+        <f>IF(COUNTA(A64:R64)=0,"",IF(COUNTBLANK(A64:R64)-IF(A64="결승",IF(B64="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A64:R64)-IF(A64="결승",IF(B64="",1,0),0))&amp;"개",IF(D64=E64,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A65" s="7"/>
       <c r="B65" s="7"/>
       <c r="C65" s="11"/>
@@ -6903,28 +6624,24 @@
       <c r="O65" s="12"/>
       <c r="P65" s="7"/>
       <c r="Q65" s="7"/>
-      <c r="R65" s="12"/>
-      <c r="S65" s="12"/>
-      <c r="T65" s="7"/>
-      <c r="U65" s="7"/>
-      <c r="V65" s="7"/>
-      <c r="W65" s="13"/>
-      <c r="X65" s="14"/>
-      <c r="Y65" s="15"/>
-      <c r="Z65" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AA65" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AB65" s="16" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="66" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R65" s="7"/>
+      <c r="S65" s="13"/>
+      <c r="T65" s="14"/>
+      <c r="U65" s="15"/>
+      <c r="V65" s="16" t="str">
+        <f>IF(A65="","",IF(A65="결승","PO-FINAL",IF(B65="","번호 없음",IF(A65="PO","PO-"&amp;B65&amp;"M",A65&amp;"-"&amp;B65&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W65" s="16" t="str">
+        <f>IF(C65="","",IFERROR(CHOOSE(WEEKDAY(C65),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X65" s="16" t="str">
+        <f>IF(COUNTA(A65:R65)=0,"",IF(COUNTBLANK(A65:R65)-IF(A65="결승",IF(B65="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A65:R65)-IF(A65="결승",IF(B65="",1,0),0))&amp;"개",IF(D65=E65,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A66" s="7"/>
       <c r="B66" s="7"/>
       <c r="C66" s="11"/>
@@ -6942,28 +6659,24 @@
       <c r="O66" s="12"/>
       <c r="P66" s="7"/>
       <c r="Q66" s="7"/>
-      <c r="R66" s="12"/>
-      <c r="S66" s="12"/>
-      <c r="T66" s="7"/>
-      <c r="U66" s="7"/>
-      <c r="V66" s="7"/>
-      <c r="W66" s="13"/>
-      <c r="X66" s="14"/>
-      <c r="Y66" s="15"/>
-      <c r="Z66" s="16" t="str">
-        <f t="shared" ref="Z66:Z81" si="6">IF(A66="","",IF(A66="결승","PO-FINAL",IF(B66="","번호 없음",IF(A66="PO","PO-"&amp;B66&amp;"M",A66&amp;"-"&amp;B66&amp;"M"))))</f>
-        <v/>
-      </c>
-      <c r="AA66" s="16" t="str">
-        <f t="shared" ref="AA66:AA81" si="7">IF(C66="","",IFERROR(CHOOSE(WEEKDAY(C66),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
-        <v/>
-      </c>
-      <c r="AB66" s="16" t="str">
-        <f t="shared" ref="AB66:AB81" si="8">IF(COUNTA(A66:V66)=0,"",IF(COUNTBLANK(A66:V66)-IF(A66="결승",IF(B66="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A66:V66)-IF(A66="결승",IF(B66="",1,0),0))&amp;"개",IF(D66=E66,"홈·원정 같음","OK")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R66" s="7"/>
+      <c r="S66" s="13"/>
+      <c r="T66" s="14"/>
+      <c r="U66" s="15"/>
+      <c r="V66" s="16" t="str">
+        <f>IF(A66="","",IF(A66="결승","PO-FINAL",IF(B66="","번호 없음",IF(A66="PO","PO-"&amp;B66&amp;"M",A66&amp;"-"&amp;B66&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W66" s="16" t="str">
+        <f>IF(C66="","",IFERROR(CHOOSE(WEEKDAY(C66),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X66" s="16" t="str">
+        <f>IF(COUNTA(A66:R66)=0,"",IF(COUNTBLANK(A66:R66)-IF(A66="결승",IF(B66="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A66:R66)-IF(A66="결승",IF(B66="",1,0),0))&amp;"개",IF(D66=E66,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A67" s="7"/>
       <c r="B67" s="7"/>
       <c r="C67" s="11"/>
@@ -6981,28 +6694,24 @@
       <c r="O67" s="12"/>
       <c r="P67" s="7"/>
       <c r="Q67" s="7"/>
-      <c r="R67" s="12"/>
-      <c r="S67" s="12"/>
-      <c r="T67" s="7"/>
-      <c r="U67" s="7"/>
-      <c r="V67" s="7"/>
-      <c r="W67" s="13"/>
-      <c r="X67" s="14"/>
-      <c r="Y67" s="15"/>
-      <c r="Z67" s="16" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AA67" s="16" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB67" s="16" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="68" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R67" s="7"/>
+      <c r="S67" s="13"/>
+      <c r="T67" s="14"/>
+      <c r="U67" s="15"/>
+      <c r="V67" s="16" t="str">
+        <f>IF(A67="","",IF(A67="결승","PO-FINAL",IF(B67="","번호 없음",IF(A67="PO","PO-"&amp;B67&amp;"M",A67&amp;"-"&amp;B67&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W67" s="16" t="str">
+        <f>IF(C67="","",IFERROR(CHOOSE(WEEKDAY(C67),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X67" s="16" t="str">
+        <f>IF(COUNTA(A67:R67)=0,"",IF(COUNTBLANK(A67:R67)-IF(A67="결승",IF(B67="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A67:R67)-IF(A67="결승",IF(B67="",1,0),0))&amp;"개",IF(D67=E67,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A68" s="7"/>
       <c r="B68" s="7"/>
       <c r="C68" s="11"/>
@@ -7020,28 +6729,24 @@
       <c r="O68" s="12"/>
       <c r="P68" s="7"/>
       <c r="Q68" s="7"/>
-      <c r="R68" s="12"/>
-      <c r="S68" s="12"/>
-      <c r="T68" s="7"/>
-      <c r="U68" s="7"/>
-      <c r="V68" s="7"/>
-      <c r="W68" s="13"/>
-      <c r="X68" s="14"/>
-      <c r="Y68" s="15"/>
-      <c r="Z68" s="16" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AA68" s="16" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB68" s="16" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="69" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R68" s="7"/>
+      <c r="S68" s="13"/>
+      <c r="T68" s="14"/>
+      <c r="U68" s="15"/>
+      <c r="V68" s="16" t="str">
+        <f>IF(A68="","",IF(A68="결승","PO-FINAL",IF(B68="","번호 없음",IF(A68="PO","PO-"&amp;B68&amp;"M",A68&amp;"-"&amp;B68&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W68" s="16" t="str">
+        <f>IF(C68="","",IFERROR(CHOOSE(WEEKDAY(C68),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X68" s="16" t="str">
+        <f>IF(COUNTA(A68:R68)=0,"",IF(COUNTBLANK(A68:R68)-IF(A68="결승",IF(B68="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A68:R68)-IF(A68="결승",IF(B68="",1,0),0))&amp;"개",IF(D68=E68,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A69" s="7"/>
       <c r="B69" s="7"/>
       <c r="C69" s="11"/>
@@ -7059,28 +6764,24 @@
       <c r="O69" s="12"/>
       <c r="P69" s="7"/>
       <c r="Q69" s="7"/>
-      <c r="R69" s="12"/>
-      <c r="S69" s="12"/>
-      <c r="T69" s="7"/>
-      <c r="U69" s="7"/>
-      <c r="V69" s="7"/>
-      <c r="W69" s="13"/>
-      <c r="X69" s="14"/>
-      <c r="Y69" s="15"/>
-      <c r="Z69" s="16" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AA69" s="16" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB69" s="16" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="70" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R69" s="7"/>
+      <c r="S69" s="13"/>
+      <c r="T69" s="14"/>
+      <c r="U69" s="15"/>
+      <c r="V69" s="16" t="str">
+        <f>IF(A69="","",IF(A69="결승","PO-FINAL",IF(B69="","번호 없음",IF(A69="PO","PO-"&amp;B69&amp;"M",A69&amp;"-"&amp;B69&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W69" s="16" t="str">
+        <f>IF(C69="","",IFERROR(CHOOSE(WEEKDAY(C69),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X69" s="16" t="str">
+        <f>IF(COUNTA(A69:R69)=0,"",IF(COUNTBLANK(A69:R69)-IF(A69="결승",IF(B69="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A69:R69)-IF(A69="결승",IF(B69="",1,0),0))&amp;"개",IF(D69=E69,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
       <c r="C70" s="11"/>
@@ -7098,28 +6799,24 @@
       <c r="O70" s="12"/>
       <c r="P70" s="7"/>
       <c r="Q70" s="7"/>
-      <c r="R70" s="12"/>
-      <c r="S70" s="12"/>
-      <c r="T70" s="7"/>
-      <c r="U70" s="7"/>
-      <c r="V70" s="7"/>
-      <c r="W70" s="13"/>
-      <c r="X70" s="14"/>
-      <c r="Y70" s="15"/>
-      <c r="Z70" s="16" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AA70" s="16" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB70" s="16" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="71" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R70" s="7"/>
+      <c r="S70" s="13"/>
+      <c r="T70" s="14"/>
+      <c r="U70" s="15"/>
+      <c r="V70" s="16" t="str">
+        <f>IF(A70="","",IF(A70="결승","PO-FINAL",IF(B70="","번호 없음",IF(A70="PO","PO-"&amp;B70&amp;"M",A70&amp;"-"&amp;B70&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W70" s="16" t="str">
+        <f>IF(C70="","",IFERROR(CHOOSE(WEEKDAY(C70),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X70" s="16" t="str">
+        <f>IF(COUNTA(A70:R70)=0,"",IF(COUNTBLANK(A70:R70)-IF(A70="결승",IF(B70="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A70:R70)-IF(A70="결승",IF(B70="",1,0),0))&amp;"개",IF(D70=E70,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A71" s="7"/>
       <c r="B71" s="7"/>
       <c r="C71" s="11"/>
@@ -7137,28 +6834,24 @@
       <c r="O71" s="12"/>
       <c r="P71" s="7"/>
       <c r="Q71" s="7"/>
-      <c r="R71" s="12"/>
-      <c r="S71" s="12"/>
-      <c r="T71" s="7"/>
-      <c r="U71" s="7"/>
-      <c r="V71" s="7"/>
-      <c r="W71" s="13"/>
-      <c r="X71" s="14"/>
-      <c r="Y71" s="15"/>
-      <c r="Z71" s="16" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AA71" s="16" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB71" s="16" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="72" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R71" s="7"/>
+      <c r="S71" s="13"/>
+      <c r="T71" s="14"/>
+      <c r="U71" s="15"/>
+      <c r="V71" s="16" t="str">
+        <f>IF(A71="","",IF(A71="결승","PO-FINAL",IF(B71="","번호 없음",IF(A71="PO","PO-"&amp;B71&amp;"M",A71&amp;"-"&amp;B71&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W71" s="16" t="str">
+        <f>IF(C71="","",IFERROR(CHOOSE(WEEKDAY(C71),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X71" s="16" t="str">
+        <f>IF(COUNTA(A71:R71)=0,"",IF(COUNTBLANK(A71:R71)-IF(A71="결승",IF(B71="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A71:R71)-IF(A71="결승",IF(B71="",1,0),0))&amp;"개",IF(D71=E71,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A72" s="7"/>
       <c r="B72" s="7"/>
       <c r="C72" s="11"/>
@@ -7176,28 +6869,24 @@
       <c r="O72" s="12"/>
       <c r="P72" s="7"/>
       <c r="Q72" s="7"/>
-      <c r="R72" s="12"/>
-      <c r="S72" s="12"/>
-      <c r="T72" s="7"/>
-      <c r="U72" s="7"/>
-      <c r="V72" s="7"/>
-      <c r="W72" s="13"/>
-      <c r="X72" s="14"/>
-      <c r="Y72" s="15"/>
-      <c r="Z72" s="16" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AA72" s="16" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB72" s="16" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="73" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R72" s="7"/>
+      <c r="S72" s="13"/>
+      <c r="T72" s="14"/>
+      <c r="U72" s="15"/>
+      <c r="V72" s="16" t="str">
+        <f>IF(A72="","",IF(A72="결승","PO-FINAL",IF(B72="","번호 없음",IF(A72="PO","PO-"&amp;B72&amp;"M",A72&amp;"-"&amp;B72&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W72" s="16" t="str">
+        <f>IF(C72="","",IFERROR(CHOOSE(WEEKDAY(C72),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X72" s="16" t="str">
+        <f>IF(COUNTA(A72:R72)=0,"",IF(COUNTBLANK(A72:R72)-IF(A72="결승",IF(B72="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A72:R72)-IF(A72="결승",IF(B72="",1,0),0))&amp;"개",IF(D72=E72,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A73" s="7"/>
       <c r="B73" s="7"/>
       <c r="C73" s="11"/>
@@ -7215,28 +6904,24 @@
       <c r="O73" s="12"/>
       <c r="P73" s="7"/>
       <c r="Q73" s="7"/>
-      <c r="R73" s="12"/>
-      <c r="S73" s="12"/>
-      <c r="T73" s="7"/>
-      <c r="U73" s="7"/>
-      <c r="V73" s="7"/>
-      <c r="W73" s="13"/>
-      <c r="X73" s="14"/>
-      <c r="Y73" s="15"/>
-      <c r="Z73" s="16" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AA73" s="16" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB73" s="16" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="74" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R73" s="7"/>
+      <c r="S73" s="13"/>
+      <c r="T73" s="14"/>
+      <c r="U73" s="15"/>
+      <c r="V73" s="16" t="str">
+        <f>IF(A73="","",IF(A73="결승","PO-FINAL",IF(B73="","번호 없음",IF(A73="PO","PO-"&amp;B73&amp;"M",A73&amp;"-"&amp;B73&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W73" s="16" t="str">
+        <f>IF(C73="","",IFERROR(CHOOSE(WEEKDAY(C73),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X73" s="16" t="str">
+        <f>IF(COUNTA(A73:R73)=0,"",IF(COUNTBLANK(A73:R73)-IF(A73="결승",IF(B73="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A73:R73)-IF(A73="결승",IF(B73="",1,0),0))&amp;"개",IF(D73=E73,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A74" s="7"/>
       <c r="B74" s="7"/>
       <c r="C74" s="11"/>
@@ -7254,28 +6939,24 @@
       <c r="O74" s="12"/>
       <c r="P74" s="7"/>
       <c r="Q74" s="7"/>
-      <c r="R74" s="12"/>
-      <c r="S74" s="12"/>
-      <c r="T74" s="7"/>
-      <c r="U74" s="7"/>
-      <c r="V74" s="7"/>
-      <c r="W74" s="13"/>
-      <c r="X74" s="14"/>
-      <c r="Y74" s="15"/>
-      <c r="Z74" s="16" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AA74" s="16" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB74" s="16" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="75" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R74" s="7"/>
+      <c r="S74" s="13"/>
+      <c r="T74" s="14"/>
+      <c r="U74" s="15"/>
+      <c r="V74" s="16" t="str">
+        <f>IF(A74="","",IF(A74="결승","PO-FINAL",IF(B74="","번호 없음",IF(A74="PO","PO-"&amp;B74&amp;"M",A74&amp;"-"&amp;B74&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W74" s="16" t="str">
+        <f>IF(C74="","",IFERROR(CHOOSE(WEEKDAY(C74),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X74" s="16" t="str">
+        <f>IF(COUNTA(A74:R74)=0,"",IF(COUNTBLANK(A74:R74)-IF(A74="결승",IF(B74="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A74:R74)-IF(A74="결승",IF(B74="",1,0),0))&amp;"개",IF(D74=E74,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A75" s="7"/>
       <c r="B75" s="7"/>
       <c r="C75" s="11"/>
@@ -7293,28 +6974,24 @@
       <c r="O75" s="12"/>
       <c r="P75" s="7"/>
       <c r="Q75" s="7"/>
-      <c r="R75" s="12"/>
-      <c r="S75" s="12"/>
-      <c r="T75" s="7"/>
-      <c r="U75" s="7"/>
-      <c r="V75" s="7"/>
-      <c r="W75" s="13"/>
-      <c r="X75" s="14"/>
-      <c r="Y75" s="15"/>
-      <c r="Z75" s="16" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AA75" s="16" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB75" s="16" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="76" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R75" s="7"/>
+      <c r="S75" s="13"/>
+      <c r="T75" s="14"/>
+      <c r="U75" s="15"/>
+      <c r="V75" s="16" t="str">
+        <f>IF(A75="","",IF(A75="결승","PO-FINAL",IF(B75="","번호 없음",IF(A75="PO","PO-"&amp;B75&amp;"M",A75&amp;"-"&amp;B75&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W75" s="16" t="str">
+        <f>IF(C75="","",IFERROR(CHOOSE(WEEKDAY(C75),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X75" s="16" t="str">
+        <f>IF(COUNTA(A75:R75)=0,"",IF(COUNTBLANK(A75:R75)-IF(A75="결승",IF(B75="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A75:R75)-IF(A75="결승",IF(B75="",1,0),0))&amp;"개",IF(D75=E75,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A76" s="7"/>
       <c r="B76" s="7"/>
       <c r="C76" s="11"/>
@@ -7332,28 +7009,24 @@
       <c r="O76" s="12"/>
       <c r="P76" s="7"/>
       <c r="Q76" s="7"/>
-      <c r="R76" s="12"/>
-      <c r="S76" s="12"/>
-      <c r="T76" s="7"/>
-      <c r="U76" s="7"/>
-      <c r="V76" s="7"/>
-      <c r="W76" s="13"/>
-      <c r="X76" s="14"/>
-      <c r="Y76" s="15"/>
-      <c r="Z76" s="16" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AA76" s="16" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB76" s="16" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="77" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R76" s="7"/>
+      <c r="S76" s="13"/>
+      <c r="T76" s="14"/>
+      <c r="U76" s="15"/>
+      <c r="V76" s="16" t="str">
+        <f>IF(A76="","",IF(A76="결승","PO-FINAL",IF(B76="","번호 없음",IF(A76="PO","PO-"&amp;B76&amp;"M",A76&amp;"-"&amp;B76&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W76" s="16" t="str">
+        <f>IF(C76="","",IFERROR(CHOOSE(WEEKDAY(C76),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X76" s="16" t="str">
+        <f>IF(COUNTA(A76:R76)=0,"",IF(COUNTBLANK(A76:R76)-IF(A76="결승",IF(B76="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A76:R76)-IF(A76="결승",IF(B76="",1,0),0))&amp;"개",IF(D76=E76,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A77" s="7"/>
       <c r="B77" s="7"/>
       <c r="C77" s="11"/>
@@ -7371,28 +7044,24 @@
       <c r="O77" s="12"/>
       <c r="P77" s="7"/>
       <c r="Q77" s="7"/>
-      <c r="R77" s="12"/>
-      <c r="S77" s="12"/>
-      <c r="T77" s="7"/>
-      <c r="U77" s="7"/>
-      <c r="V77" s="7"/>
-      <c r="W77" s="13"/>
-      <c r="X77" s="14"/>
-      <c r="Y77" s="15"/>
-      <c r="Z77" s="16" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AA77" s="16" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB77" s="16" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="78" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R77" s="7"/>
+      <c r="S77" s="13"/>
+      <c r="T77" s="14"/>
+      <c r="U77" s="15"/>
+      <c r="V77" s="16" t="str">
+        <f>IF(A77="","",IF(A77="결승","PO-FINAL",IF(B77="","번호 없음",IF(A77="PO","PO-"&amp;B77&amp;"M",A77&amp;"-"&amp;B77&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W77" s="16" t="str">
+        <f>IF(C77="","",IFERROR(CHOOSE(WEEKDAY(C77),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X77" s="16" t="str">
+        <f>IF(COUNTA(A77:R77)=0,"",IF(COUNTBLANK(A77:R77)-IF(A77="결승",IF(B77="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A77:R77)-IF(A77="결승",IF(B77="",1,0),0))&amp;"개",IF(D77=E77,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A78" s="7"/>
       <c r="B78" s="7"/>
       <c r="C78" s="11"/>
@@ -7410,28 +7079,24 @@
       <c r="O78" s="12"/>
       <c r="P78" s="7"/>
       <c r="Q78" s="7"/>
-      <c r="R78" s="12"/>
-      <c r="S78" s="12"/>
-      <c r="T78" s="7"/>
-      <c r="U78" s="7"/>
-      <c r="V78" s="7"/>
-      <c r="W78" s="13"/>
-      <c r="X78" s="14"/>
-      <c r="Y78" s="15"/>
-      <c r="Z78" s="16" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AA78" s="16" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB78" s="16" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="79" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R78" s="7"/>
+      <c r="S78" s="13"/>
+      <c r="T78" s="14"/>
+      <c r="U78" s="15"/>
+      <c r="V78" s="16" t="str">
+        <f>IF(A78="","",IF(A78="결승","PO-FINAL",IF(B78="","번호 없음",IF(A78="PO","PO-"&amp;B78&amp;"M",A78&amp;"-"&amp;B78&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W78" s="16" t="str">
+        <f>IF(C78="","",IFERROR(CHOOSE(WEEKDAY(C78),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X78" s="16" t="str">
+        <f>IF(COUNTA(A78:R78)=0,"",IF(COUNTBLANK(A78:R78)-IF(A78="결승",IF(B78="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A78:R78)-IF(A78="결승",IF(B78="",1,0),0))&amp;"개",IF(D78=E78,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A79" s="7"/>
       <c r="B79" s="7"/>
       <c r="C79" s="11"/>
@@ -7449,28 +7114,24 @@
       <c r="O79" s="12"/>
       <c r="P79" s="7"/>
       <c r="Q79" s="7"/>
-      <c r="R79" s="12"/>
-      <c r="S79" s="12"/>
-      <c r="T79" s="7"/>
-      <c r="U79" s="7"/>
-      <c r="V79" s="7"/>
-      <c r="W79" s="13"/>
-      <c r="X79" s="14"/>
-      <c r="Y79" s="15"/>
-      <c r="Z79" s="16" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AA79" s="16" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB79" s="16" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="80" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R79" s="7"/>
+      <c r="S79" s="13"/>
+      <c r="T79" s="14"/>
+      <c r="U79" s="15"/>
+      <c r="V79" s="16" t="str">
+        <f>IF(A79="","",IF(A79="결승","PO-FINAL",IF(B79="","번호 없음",IF(A79="PO","PO-"&amp;B79&amp;"M",A79&amp;"-"&amp;B79&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W79" s="16" t="str">
+        <f>IF(C79="","",IFERROR(CHOOSE(WEEKDAY(C79),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X79" s="16" t="str">
+        <f>IF(COUNTA(A79:R79)=0,"",IF(COUNTBLANK(A79:R79)-IF(A79="결승",IF(B79="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A79:R79)-IF(A79="결승",IF(B79="",1,0),0))&amp;"개",IF(D79=E79,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A80" s="7"/>
       <c r="B80" s="7"/>
       <c r="C80" s="11"/>
@@ -7488,28 +7149,24 @@
       <c r="O80" s="12"/>
       <c r="P80" s="7"/>
       <c r="Q80" s="7"/>
-      <c r="R80" s="12"/>
-      <c r="S80" s="12"/>
-      <c r="T80" s="7"/>
-      <c r="U80" s="7"/>
-      <c r="V80" s="7"/>
-      <c r="W80" s="13"/>
-      <c r="X80" s="14"/>
-      <c r="Y80" s="15"/>
-      <c r="Z80" s="16" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AA80" s="16" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB80" s="16" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="81" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="R80" s="7"/>
+      <c r="S80" s="13"/>
+      <c r="T80" s="14"/>
+      <c r="U80" s="15"/>
+      <c r="V80" s="16" t="str">
+        <f>IF(A80="","",IF(A80="결승","PO-FINAL",IF(B80="","번호 없음",IF(A80="PO","PO-"&amp;B80&amp;"M",A80&amp;"-"&amp;B80&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W80" s="16" t="str">
+        <f>IF(C80="","",IFERROR(CHOOSE(WEEKDAY(C80),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X80" s="16" t="str">
+        <f>IF(COUNTA(A80:R80)=0,"",IF(COUNTBLANK(A80:R80)-IF(A80="결승",IF(B80="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A80:R80)-IF(A80="결승",IF(B80="",1,0),0))&amp;"개",IF(D80=E80,"홈·원정 같음","OK")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A81" s="7"/>
       <c r="B81" s="7"/>
       <c r="C81" s="11"/>
@@ -7527,36 +7184,32 @@
       <c r="O81" s="12"/>
       <c r="P81" s="7"/>
       <c r="Q81" s="7"/>
-      <c r="R81" s="12"/>
-      <c r="S81" s="12"/>
-      <c r="T81" s="7"/>
-      <c r="U81" s="7"/>
-      <c r="V81" s="7"/>
-      <c r="W81" s="13"/>
-      <c r="X81" s="14"/>
-      <c r="Y81" s="15"/>
-      <c r="Z81" s="16" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AA81" s="16" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB81" s="16" t="str">
-        <f t="shared" si="8"/>
+      <c r="R81" s="7"/>
+      <c r="S81" s="13"/>
+      <c r="T81" s="14"/>
+      <c r="U81" s="15"/>
+      <c r="V81" s="16" t="str">
+        <f>IF(A81="","",IF(A81="결승","PO-FINAL",IF(B81="","번호 없음",IF(A81="PO","PO-"&amp;B81&amp;"M",A81&amp;"-"&amp;B81&amp;"M"))))</f>
+        <v/>
+      </c>
+      <c r="W81" s="16" t="str">
+        <f>IF(C81="","",IFERROR(CHOOSE(WEEKDAY(C81),"일","월","화","수","목","금","토"),"날짜 확인"))</f>
+        <v/>
+      </c>
+      <c r="X81" s="16" t="str">
+        <f>IF(COUNTA(A81:R81)=0,"",IF(COUNTBLANK(A81:R81)-IF(A81="결승",IF(B81="",1,0),0)&gt;0,"빈칸 "&amp;(COUNTBLANK(A81:R81)-IF(A81="결승",IF(B81="",1,0),0))&amp;"개",IF(D81=E81,"홈·원정 같음","OK")))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB81"/>
+  <autoFilter ref="A1:X81"/>
   <phoneticPr fontId="8" type="noConversion"/>
-  <conditionalFormatting sqref="AB2:AB81">
+  <conditionalFormatting sqref="X2:X81">
     <cfRule type="expression" dxfId="1" priority="1">
-      <formula>AND(AB2&lt;&gt;"",AB2&lt;&gt;"OK")</formula>
+      <formula>AND(X2&lt;&gt;"",X2&lt;&gt;"OK")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="2">
-      <formula>AB2="OK"</formula>
+      <formula>X2="OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
@@ -7570,7 +7223,7 @@
     <dataValidation type="date" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="날짜" error="날짜로 넣어 주세요. 예: 10/4 또는 2026-10-04" sqref="C2:C81">
       <formula1>44927</formula1>
     </dataValidation>
-    <dataValidation type="time" allowBlank="1" showErrorMessage="1" errorTitle="시간" error="시간으로 넣어 주세요. 예: 21:00" sqref="W2:W81"/>
+    <dataValidation type="time" allowBlank="1" showErrorMessage="1" errorTitle="시간" error="시간으로 넣어 주세요. 예: 21:00" sqref="S2:S81"/>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing r:id="rId1"/>
@@ -7587,13 +7240,13 @@
           <x14:formula1>
             <xm:f>목록!$D$2:$D$10</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F81 H2:H81 J2:J81 L2:L81 N2:N81 P2:P81 R2:R81 T2:T81</xm:sqref>
+          <xm:sqref>F2:F81 H2:H81 J2:J81 L2:L81 N2:N81 P2:P81</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="맵" error="'목록' 시트 B열의 맵에서 골라 주세요.">
           <x14:formula1>
             <xm:f>목록!$B$2:$B$31</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:G81 I2:I81 K2:K81 M2:M81 O2:O81 Q2:Q81 S2:S81 U2:U81 V2:V81</xm:sqref>
+          <xm:sqref>G2:G81 I2:I81 K2:K81 M2:M81 O2:O81 Q2:Q81 R2:R81</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -7614,154 +7267,154 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="17"/>
       <c r="B2" s="17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F2" s="19" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="17"/>
       <c r="B3" s="17" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="17"/>
       <c r="B5" s="17" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="17"/>
       <c r="B6" s="17" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="17"/>
       <c r="B7" s="17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="17"/>
       <c r="B8" s="17" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="17"/>
       <c r="B9" s="17" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="17"/>
       <c r="B10" s="17" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="17"/>
       <c r="B11" s="17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="17"/>
       <c r="B12" s="17" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="17"/>
       <c r="B13" s="17" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
